--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0021.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0021.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Đối thủ đã Triển Khai xong. Bạn có thể xem Triển Khai của họ ngay bây giờ.</t>
+          <t>Đối thủ đã triển khai xong. Giờ cậu có thể xem Đội Hình của họ.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Đây là Khu Triển Khai của bạn. Nó có 6 Vị Trí và 1 Khu Biến Hình.</t>
+          <t>Đây là Khu Triển Khai của cậu. Có 6 Ô và 1 Khu Biến Hóa.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Đây là Khu Triển Khai của bạn. Nó có 6 Vị Trí và 1 Khu Biến Hình.</t>
+          <t>Đây là Khu Triển Khai của cậu. Có 6 Ô và 1 Khu Biến Hóa.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Đây là Khu Triển Khai của bạn. Nó có 6 Vị Trí và 1 Khu Biến Hình.</t>
+          <t>Đây là Khu Triển Khai của cậu. Có 6 Ô và 1 Khu Biến Hóa.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Đây là Khu Vực Tay Cầm. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem các lá bài bạn đang cầm trên tay.</t>
+          <t>Đây là Khu Tay Cầm của cậu. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các thẻ cậu đang giữ.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{0} Đây là Khu Vực Trong Tay. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem các thẻ cậu đang giữ.</t>
+          <t>{0} Đây là Khu Vực Trên Tay của cậu. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các lá bài trên tay.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Đây là Khu Vực Tay Cầm. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem các lá bài bạn đang cầm trên tay.</t>
+          <t>Đây là Khu Tay Cầm của cậu. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các thẻ cậu đang giữ.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{0} Chọn một Echo để xem chi tiết.</t>
+          <t>Chọn một Echo để xem chi tiết.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Thông tin cơ bản về chỉ số và cấp độ của Echo được hiển thị tại đây.</t>
+          <t>Thông tin cơ bản về chỉ số và cấp độ của Echo hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Thông tin cơ bản về chỉ số và cấp độ của Echo được hiển thị tại đây.</t>
+          <t>Thông tin cơ bản về chỉ số và cấp độ của Echo hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Thông tin cơ bản về chỉ số và cấp độ của Echo được hiển thị tại đây.</t>
+          <t>Thông tin cơ bản về chỉ số và cấp độ của Echo hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Triệu hồi Echo tiêu hao Energy. Energy tái tạo khi bắt đầu mỗi lượt.</t>
+          <t>Triệu hồi Echo sẽ tiêu hao Năng Lượng. Năng Lượng sẽ hồi lại vào đầu mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Triệu hồi Echo tiêu hao Energy. Energy tái tạo khi bắt đầu mỗi lượt.</t>
+          <t>Triệu hồi Echo sẽ tiêu hao Năng Lượng. Năng Lượng sẽ hồi lại vào đầu mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Triệu hồi Echo tiêu hao Energy. Energy tái tạo khi bắt đầu mỗi lượt.</t>
+          <t>Triệu hồi Echo sẽ tiêu hao Năng Lượng. Năng Lượng sẽ hồi lại vào đầu mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Place Electro Predator vào đây. Các Echoes ở bên phải sẽ xuất hiện ở Hàng Sau.</t>
+          <t>Đặt Electro Predator vào đây. Các Echo ở phía bên phải sẽ xuất hiện ở Hàng Sau.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Place Electro Predator vào đây. Các Echoes ở bên phải sẽ xuất hiện ở Hàng Sau.</t>
+          <t>Đặt Electro Predator vào đây. Các Echo ở phía bên phải sẽ xuất hiện ở Hàng Sau.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Place Electro Predator vào đây. Các Echoes ở bên phải sẽ xuất hiện ở Hàng Sau.</t>
+          <t>Đặt Electro Predator vào đây. Các Echo ở phía bên phải sẽ xuất hiện ở Hàng Sau.</t>
         </is>
       </c>
     </row>
@@ -2005,8 +2005,8 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để vào Battle Stage.
-Năng Lượng chưa dùng sẽ không được bảo lưu cho vòng tiếp theo.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào Giai Đoạn Chiến Đấu.
+Năng lượng chưa sử dụng sẽ không được bảo lưu cho vòng tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -2072,8 +2072,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{0} Giữ để vào Battle Stage.
-Năng lượng chưa sử dụng sẽ không được bảo lưu cho vòng tiếp theo.</t>
+          <t>Giữ để vào Giai Đoạn Chiến Đấu.
+Năng lượng không sử dụng sẽ không được bảo lưu cho lượt sau.</t>
         </is>
       </c>
     </row>
@@ -2139,8 +2139,8 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để vào Battle Stage.
-Năng lượng chưa dùng sẽ không được bảo lưu cho vòng tiếp theo.</t>
+          <t>Nhấn vào đây để vào Giai Đoạn Chiến Đấu.
+Năng lượng không sử dụng sẽ không được bảo lưu cho lượt tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Echoes của cậu đã thắng trận đấu vừa rồi.</t>
+          <t>Echo của cậu đã thắng trận đấu trước.</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Echoes của cậu đã thắng trận đấu vừa rồi.</t>
+          <t>Echo của cậu đã thắng trận đấu trước.</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Echoes của cậu đã thắng trận đấu vừa rồi.</t>
+          <t>Echo của cậu đã thắng trận đấu trước.</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Sau khi thắng Battle Stage, các Echoes còn sống sẽ gây sát thương lên đối thủ. Chiến thắng sẽ đến khi HP của đối thủ giảm về 0.</t>
+          <t>Sau khi thắng Battle Stage, những Echo còn sống sẽ gây sát thương lên đối thủ. Chiến thắng sẽ đến khi HP của đối thủ về 0.</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Sau khi thắng Battle Stage, các Echoes còn sống sẽ gây sát thương lên đối thủ. Chiến thắng sẽ đến khi HP của đối thủ giảm về 0.</t>
+          <t>Sau khi thắng Battle Stage, những Echo còn sống sẽ gây sát thương lên đối thủ. Chiến thắng sẽ đến khi HP của đối thủ về 0.</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Sau khi thắng Battle Stage, các Echoes còn sống sẽ gây sát thương lên đối thủ. Chiến thắng sẽ đến khi HP của đối thủ giảm về 0.</t>
+          <t>Sau khi thắng Battle Stage, những Echo còn sống sẽ gây sát thương lên đối thủ. Chiến thắng sẽ đến khi HP của đối thủ về 0.</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Triệu hồi thêm 2 Echoes để tăng cường phe bạn.</t>
+          <t>Triệu hồi thêm hai Echo nữa để tăng cường phe ta.</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Triệu hồi thêm 2 Echoes để tăng cường phe bạn.</t>
+          <t>Triệu hồi thêm hai Echo nữa để tăng cường phe ta.</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Triệu hồi thêm 2 Echoes để tăng cường phe bạn.</t>
+          <t>Triệu hồi thêm hai Echo nữa để tăng cường phe ta.</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Năng lượng của cậu đã phục hồi. Triển khai thêm Echoes để đánh bại đối thủ.</t>
+          <t>Năng lượng của cậu đã hồi phục. Triệu hồi thêm Echo để đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Năng lượng của cậu đã phục hồi. Triển khai thêm Echoes để đánh bại đối thủ.</t>
+          <t>Năng lượng của cậu đã hồi phục. Triệu hồi thêm Echo để đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Năng lượng của cậu đã phục hồi. Triển khai thêm Echoes để đánh bại đối thủ.</t>
+          <t>Năng lượng của cậu đã hồi phục. Triệu hồi thêm Echo để đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Giai đoạn Triển Khai đã kết thúc. Giai đoạn Chiến Đấu sắp bắt đầu.</t>
+          <t>Giai Đoạn Triển Khai đã kết thúc. Giai Đoạn Chiến Đấu sắp bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Giai Đoạn Triển Khai đã kết thúc. Giữ {0} để bắt đầu Battle Stage.</t>
+          <t>Giai Đoạn Triển Khai đã kết thúc. Giữ {0} để bắt đầu Giai Đoạn Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Giai đoạn Triển Khai đã kết thúc. Giai đoạn Chiến Đấu sắp bắt đầu.</t>
+          <t>Giai Đoạn Triển Khai đã kết thúc. Giai Đoạn Chiến Đấu sắp bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#8c7e51&gt;Skills Special&lt;/color&gt; và &lt;color=#8c7e51&gt;Modulation&lt;/color&gt; sẽ tăng đáng kể sức chiến đấu của Echo.</t>
+          <t>Sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; và &lt;color=#8c7e51&gt;Điều Chỉnh&lt;/color&gt; sẽ tăng sức chiến đấu của Echo lên rất nhiều.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#8c7e51&gt;Skills Special&lt;/color&gt; và &lt;color=#8c7e51&gt;Modulation&lt;/color&gt; sẽ tăng đáng kể sức chiến đấu của Echo.</t>
+          <t>Sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; và &lt;color=#8c7e51&gt;Điều Chỉnh&lt;/color&gt; sẽ tăng sức chiến đấu của Echo lên rất nhiều.</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#8c7e51&gt;Skills Special&lt;/color&gt; và &lt;color=#8c7e51&gt;Modulation&lt;/color&gt; sẽ tăng đáng kể sức chiến đấu của Echo.</t>
+          <t>Sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; và &lt;color=#8c7e51&gt;Điều Chỉnh&lt;/color&gt; sẽ tăng sức chiến đấu của Echo lên rất nhiều.</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Một số Echoes có Special Skill bị vô hiệu khi mới triển khai. Tuy nhiên, sau khi Modulation, &lt;color=#8c7e51&gt;Special Skill của chúng sẽ được kế thừa bởi Echoes mới&lt;/color&gt; và trở nên hoạt động.</t>
+          <t>Một số Echo có Kỹ Năng Đặc Biệt ở trạng thái bất hoạt khi mới Triệu Hồi. Nhưng sau khi Điều Chế, &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt đó sẽ được kế thừa bởi một Echo mới&lt;/color&gt; và trở nên hoạt động.</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Một số Echoes có Special Skill bị vô hiệu khi mới triển khai. Tuy nhiên, sau khi Modulation, &lt;color=#8c7e51&gt;Special Skill của chúng sẽ được kế thừa bởi Echoes mới&lt;/color&gt; và trở nên hoạt động.</t>
+          <t>Một số Echo có Kỹ Năng Đặc Biệt ở trạng thái bất hoạt khi mới Triệu Hồi. Nhưng sau khi Điều Chế, &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt đó sẽ được kế thừa bởi một Echo mới&lt;/color&gt; và trở nên hoạt động.</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Một số Echoes có Special Skill bị vô hiệu khi mới triển khai. Tuy nhiên, sau khi Modulation, &lt;color=#8c7e51&gt;Special Skill của chúng sẽ được kế thừa bởi Echoes mới&lt;/color&gt; và trở nên hoạt động.</t>
+          <t>Một số Echo có Kỹ Năng Đặc Biệt ở trạng thái bất hoạt khi mới Triệu Hồi. Nhưng sau khi Điều Chế, &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt đó sẽ được kế thừa bởi một Echo mới&lt;/color&gt; và trở nên hoạt động.</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Kéo Fusion Warrior sang bên trái của Khu Triển Khai.</t>
+          <t>Kéo Chiến Binh Fusion sang phía trái của Khu Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Kéo Fusion Warrior sang bên trái của Khu Triển Khai.</t>
+          <t>Kéo Chiến Binh Fusion sang phía trái của Khu Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Kéo Fusion Warrior sang bên trái của Khu Triển Khai.</t>
+          <t>Kéo Chiến Binh Fusion sang phía trái của Khu Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Modulation thành công. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} để kiểm tra Kỹ Năng Special đã kế thừa và kích hoạt.</t>
+          <t>Điều biến thành công. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra Kỹ Năng Đặc Biệt đã kế thừa và kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Modulation thành công. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} {0} để kiểm tra Kỹ Năng Special đã kế thừa và kích hoạt.</t>
+          <t>Điều biến thành công. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} {0} để kiểm tra Kỹ Năng Đặc Biệt đã kế thừa và kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Modulation thành công. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} để kiểm tra Kỹ Năng Special đã kế thừa và kích hoạt.</t>
+          <t>Điều biến thành công. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra Kỹ Năng Đặc Biệt đã kế thừa và kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Echo mới &lt;color=#8c7e51&gt;đã kế thừa&lt;/color&gt; &lt;color=#8c7e51&gt;Kỹ Năng Special&lt;/color&gt; của Echo trước đó. Kỹ Năng Special hiện đã được kích hoạt cho Echo mới.</t>
+          <t>Echo mới đã &lt;color=#8c7e51&gt;thừa hưởng&lt;/color&gt; &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; từ Echo trước. Kỹ Năng Đặc Biệt hiện đã được kích hoạt cho Echo mới.</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Echo mới &lt;color=#8c7e51&gt;đã kế thừa&lt;/color&gt; &lt;color=#8c7e51&gt;Kỹ Năng Special&lt;/color&gt; của Echo trước đó. Kỹ Năng Special hiện đã được kích hoạt cho Echo mới.</t>
+          <t>Echo mới đã &lt;color=#8c7e51&gt;thừa hưởng&lt;/color&gt; &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; từ Echo trước. Kỹ Năng Đặc Biệt hiện đã được kích hoạt cho Echo mới.</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Echo mới &lt;color=#8c7e51&gt;đã kế thừa&lt;/color&gt; &lt;color=#8c7e51&gt;Kỹ Năng Special&lt;/color&gt; của Echo trước đó. Kỹ Năng Special hiện đã được kích hoạt cho Echo mới.</t>
+          <t>Echo mới đã &lt;color=#8c7e51&gt;thừa hưởng&lt;/color&gt; &lt;color=#8c7e51&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; từ Echo trước. Kỹ Năng Đặc Biệt hiện đã được kích hoạt cho Echo mới.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kỹ Năng Special của Fusion Warrior đã kích hoạt. Hãy dùng nó để giành chiến thắng trong cuộc đấu!</t>
+          <t>Kỹ Năng Đặc Biệt của Chiến Binh Fusion đã kích hoạt. Hãy sử dụng nó để giành chiến thắng trong cuộc đấu!</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{0} Skill đặc biệt của Chiến binh Fusion đã kích hoạt. Hãy dùng nó để giành chiến thắng trong cuộc đấu!</t>
+          <t>{0} Kỹ Năng Đặc Biệt của Chiến Binh Fusion đã sẵn sàng. Dùng nó để giành chiến thắng trong trận đấu nhé!</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kỹ Năng Special của Fusion Warrior đã kích hoạt. Hãy dùng nó để giành chiến thắng trong cuộc đấu!</t>
+          <t>Kỹ Năng Đặc Biệt của Chiến Binh Fusion đã kích hoạt. Hãy sử dụng nó để giành chiến thắng trong cuộc đấu!</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Chọn Baby Viridblaze Saurian để &lt;color=#8c7e51&gt;cộng dồn&lt;/color&gt; lên Fusion Warrior và bắt đầu Modulation.</t>
+          <t>Chọn Baby Viridblaze Saurian để &lt;color=#8c7e51&gt;chồng&lt;/color&gt; lên Fusion Warrior và bắt đầu Điều Chế.</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Chọn Baby Viridblaze Saurian để &lt;color=#8c7e51&gt;cộng dồn&lt;/color&gt; lên Fusion Warrior và bắt đầu Modulation.</t>
+          <t>Chọn Baby Viridblaze Saurian để &lt;color=#8c7e51&gt;chồng&lt;/color&gt; lên Fusion Warrior và bắt đầu Điều Chế.</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Chọn Baby Viridblaze Saurian để &lt;color=#8c7e51&gt;cộng dồn&lt;/color&gt; lên Fusion Warrior và bắt đầu Modulation.</t>
+          <t>Chọn Baby Viridblaze Saurian để &lt;color=#8c7e51&gt;chồng&lt;/color&gt; lên Fusion Warrior và bắt đầu Điều Chế.</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Echo này có Energy Cost là 3.</t>
+          <t>Hồi Âm này có Chi Phí Năng Lượng là 3.</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{0} Echo này có Energy Cost là 3.</t>
+          <t>{0} Tacet Discord này có Chi Phí Năng Lượng là 3.</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Echo này có Energy Cost là 3.</t>
+          <t>Hồi Âm này có Chi Phí Năng Lượng là 3.</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Để Triển khai Echo này, nó phải được xếp chồng lên trên một &lt;color=#8c7e51&gt;Modulated Echo&lt;/color&gt; để thực hiện Modulation riêng của nó.</t>
+          <t>Để triển khai Echo này, nó phải được xếp chồng lên một &lt;color=#8c7e51&gt;Modulated Echo&lt;/color&gt; khác để thực hiện Modulation của riêng nó.</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Để Triển khai Echo này, nó phải được xếp chồng lên trên một &lt;color=#8c7e51&gt;Modulated Echo&lt;/color&gt; để thực hiện Modulation riêng của nó.</t>
+          <t>Để triển khai Echo này, nó phải được xếp chồng lên một &lt;color=#8c7e51&gt;Modulated Echo&lt;/color&gt; khác để thực hiện Modulation của riêng nó.</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Để Triển khai Echo này, nó phải được xếp chồng lên trên một &lt;color=#8c7e51&gt;Modulated Echo&lt;/color&gt; để thực hiện Modulation riêng của nó.</t>
+          <t>Để triển khai Echo này, nó phải được xếp chồng lên một &lt;color=#8c7e51&gt;Modulated Echo&lt;/color&gt; khác để thực hiện Modulation của riêng nó.</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>Spearback có Chi Phí Năng Lượng là 3.
-Hiện tại ngươi không đủ Năng Lượng. Hãy Tái Cấu Trúc Vanguard Junrock để nhận thêm Năng Lượng.</t>
+Hiện tại cậu không đủ Năng Lượng. Hãy Tái Cấu Trúc Vanguard Junrock để nhận thêm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>Spearback có Chi Phí Năng Lượng là 3.
-Hiện tại ngươi không đủ Năng Lượng. Hãy Tái Cấu Trúc Vanguard Junrock để nhận thêm Năng Lượng.</t>
+Hiện tại cậu không đủ Năng Lượng. Hãy Tái Cấu Trúc Vanguard Junrock để nhận thêm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>Spearback có Chi Phí Năng Lượng là 3.
-Hiện tại ngươi không đủ Năng Lượng. Hãy Tái Cấu Trúc Vanguard Junrock để nhận thêm Năng Lượng.</t>
+Hiện tại cậu không đủ Năng Lượng. Hãy Tái Cấu Trúc Vanguard Junrock để nhận thêm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Để Triển khai Spearback, hãy xếp chồng nó lên trên Modulated Baby Viridblaze Saurian.</t>
+          <t>Để triển khai Spearback, hãy xếp nó lên trên Modulated Baby Viridblaze Saurian.</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Để Triển khai Spearback, hãy xếp chồng nó lên trên Modulated Baby Viridblaze Saurian.</t>
+          <t>Để triển khai Spearback, hãy xếp nó lên trên Modulated Baby Viridblaze Saurian.</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Để Triển khai Spearback, hãy xếp chồng nó lên trên Modulated Baby Viridblaze Saurian.</t>
+          <t>Để triển khai Spearback, hãy xếp nó lên trên Modulated Baby Viridblaze Saurian.</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Echo Mũi Giáo với Kỹ Năng Special đã được Triệu Hồi. Hãy sử dụng nó để phá vỡ phòng thủ của đối thủ.</t>
+          <t>Kẻ Đâm Lưng với Kỹ Năng Đặc Biệt đã được Triệu Hồi. Dùng nó để phá vỡ phòng tuyến của đối thủ.</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{0} Kích Ngư Special đã được Triển Khai. Hãy sử dụng nó để phá vỡ phòng thủ của đối thủ.</t>
+          <t>{0} Spearback với Kỹ Năng Đặc Biệt đã được Triệu Hồi. Dùng nó để phá vỡ phòng tuyến đối thủ.</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Echo Mũi Giáo với Kỹ Năng Special đã được Triệu Hồi. Hãy sử dụng nó để phá vỡ phòng thủ của đối thủ.</t>
+          <t>Kẻ Đâm Lưng với Kỹ Năng Đặc Biệt đã được Triệu Hồi. Dùng nó để phá vỡ phòng tuyến của đối thủ.</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Echoes có &lt;color=#8c7e51&gt;Biến Đổi Skill&lt;/color&gt; có thể hỗ trợ các Echoes khác. Trước tiên, triển khai &lt;color=#8c7e51&gt;Fusion Warrior&lt;/color&gt; lên tiền tuyến.</t>
+          <t>Echo sở hữu Kỹ Năng &lt;color=#8c7e51&gt;Biến Hình&lt;/color&gt; có thể hỗ trợ các Echo khác. Trước tiên, hãy Triển Khai &lt;color=#8c7e51&gt;Chiến Binh Fusion&lt;/color&gt; lên Hàng Tiền Tuyến.</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Echoes có &lt;color=#8c7e51&gt;Biến Đổi Skill&lt;/color&gt; có thể hỗ trợ các Echoes khác. Trước tiên, triển khai &lt;color=#8c7e51&gt;Fusion Warrior&lt;/color&gt; lên tiền tuyến.</t>
+          <t>Echo sở hữu Kỹ Năng &lt;color=#8c7e51&gt;Biến Hình&lt;/color&gt; có thể hỗ trợ các Echo khác. Trước tiên, hãy Triển Khai &lt;color=#8c7e51&gt;Chiến Binh Fusion&lt;/color&gt; lên Hàng Tiền Tuyến.</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Echoes có &lt;color=#8c7e51&gt;Biến Đổi Skill&lt;/color&gt; có thể hỗ trợ các Echoes khác. Trước tiên, triển khai &lt;color=#8c7e51&gt;Fusion Warrior&lt;/color&gt; lên tiền tuyến.</t>
+          <t>Echo sở hữu Kỹ Năng &lt;color=#8c7e51&gt;Biến Hình&lt;/color&gt; có thể hỗ trợ các Echo khác. Trước tiên, hãy Triển Khai &lt;color=#8c7e51&gt;Chiến Binh Fusion&lt;/color&gt; lên Hàng Tiền Tuyến.</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Đây là Khu Vực Biến Hóa. Kéo Echo vào đây sẽ kích hoạt Biến Đổi Skill của nó.</t>
+          <t>Đây là Khu Biến Đổi. Kéo một Echo vào đây sẽ kích hoạt Kỹ Năng Biến Đổi của nó.</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Đây là Khu Vực Biến Hóa. Kéo Echo vào đây sẽ kích hoạt Biến Đổi Skill của nó.</t>
+          <t>Đây là Khu Biến Đổi. Kéo một Echo vào đây sẽ kích hoạt Kỹ Năng Biến Đổi của nó.</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Đây là Khu Vực Biến Hóa. Kéo Echo vào đây sẽ kích hoạt Biến Đổi Skill của nó.</t>
+          <t>Đây là Khu Biến Đổi. Kéo một Echo vào đây sẽ kích hoạt Kỹ Năng Biến Đổi của nó.</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Dwarf Cassowary&lt;/color&gt; có &lt;color=#8c7e51&gt;Kỹ Năng Biến Hình&lt;/color&gt;, được kích hoạt bằng cách kéo nó vào Khu Vực Biến Hình.</t>
+          <t>&lt;color=#8c7e51&gt;Đà Điểu Lùn&lt;/color&gt; sở hữu Kỹ Năng &lt;color=#8c7e51&gt;Biến Hình&lt;/color&gt;, được kích hoạt bằng cách kéo nó vào Khu Vực Biến Hình.</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Dwarf Cassowary&lt;/color&gt; có &lt;color=#8c7e51&gt;Kỹ Năng Biến Hình&lt;/color&gt;, được kích hoạt bằng cách kéo nó vào Khu Vực Biến Hình.</t>
+          <t>&lt;color=#8c7e51&gt;Đà Điểu Lùn&lt;/color&gt; sở hữu Kỹ Năng &lt;color=#8c7e51&gt;Biến Hình&lt;/color&gt;, được kích hoạt bằng cách kéo nó vào Khu Vực Biến Hình.</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Dwarf Cassowary&lt;/color&gt; có &lt;color=#8c7e51&gt;Kỹ Năng Biến Hình&lt;/color&gt;, được kích hoạt bằng cách kéo nó vào Khu Vực Biến Hình.</t>
+          <t>&lt;color=#8c7e51&gt;Đà Điểu Lùn&lt;/color&gt; sở hữu Kỹ Năng &lt;color=#8c7e51&gt;Biến Hình&lt;/color&gt;, được kích hoạt bằng cách kéo nó vào Khu Vực Biến Hình.</t>
         </is>
       </c>
     </row>
@@ -6112,8 +6112,8 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Fusion Warrior đã được tăng cường.
-Sau khi vòng đấu kết thúc, các Echoes không sử dụng sẽ trở về bộ bài.</t>
+          <t>Chiến Binh Fusion đã được tăng cường.
+Sau khi lượt kết thúc, Echo chưa sử dụng sẽ trở lại bộ bài.</t>
         </is>
       </c>
     </row>
@@ -6179,8 +6179,8 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{0} Chiến binh Fusion đã được tăng cường.
-Sau khi vòng đấu kết thúc, các Echoes không sử dụng sẽ trở về bộ bài.</t>
+          <t>{0} Chiến Binh Fusion đã được tăng cường.
+Sau khi hiệp đấu kết thúc, các Tacet Discord không sử dụng sẽ trở về bộ bài.</t>
         </is>
       </c>
     </row>
@@ -6246,8 +6246,8 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Fusion Warrior đã được tăng cường.
-Sau khi vòng đấu kết thúc, các Echoes không sử dụng sẽ trở về bộ bài.</t>
+          <t>Chiến Binh Fusion đã được tăng cường.
+Sau khi lượt kết thúc, Echo chưa sử dụng sẽ trở lại bộ bài.</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Phép Thử đã hoàn tất. Core Echo trên tay bạn giờ có thể Triển Khai.</t>
+          <t>Thử thách hoàn tất. Core Echo trên tay cậu giờ có thể Triển Khai rồi.</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{0} Trial đã hoàn tất. Core Echo trên tay bạn giờ có thể Triển Khai.</t>
+          <t>{0} Thử thách hoàn tất. Tacet Discord Cốt Lõi trên tay cậu giờ có thể Triệu Hồi được rồi.</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Phép Thử đã hoàn tất. Core Echo trên tay bạn giờ có thể Triển Khai.</t>
+          <t>Thử thách hoàn tất. Core Echo trên tay cậu giờ có thể Triển Khai rồi.</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Triển khai Core Echo không tiêu hao Energy.</t>
+          <t>Triển khai Tâm Ảnh Cốt không tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Triển khai Core Echo không tiêu hao Energy.</t>
+          <t>Triển khai Tâm Ảnh Cốt không tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Triển khai Core Echo không tiêu hao Energy.</t>
+          <t>Triển khai Tâm Ảnh Cốt không tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -6703,8 +6703,8 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Triển khai Core Echoes.
-Core Echoes không thể Modulate hoặc Reconstruct.</t>
+          <t>Triển khai Core Echo.
+Core Echo không thể bị Điều Chỉnh hay Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -6770,8 +6770,8 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Triển khai Core Echoes.
-Core Echoes không thể Modulate hoặc Reconstruct.</t>
+          <t>Triển khai Core Echo.
+Core Echo không thể bị Điều Chỉnh hay Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -6837,8 +6837,8 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Triển khai Core Echoes.
-Core Echoes không thể Modulate hoặc Reconstruct.</t>
+          <t>Triển khai Core Echo.
+Core Echo không thể bị Điều Chỉnh hay Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Tiêu diệt kẻ địch và giành chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Tiêu diệt kẻ địch và giành chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Tiêu diệt kẻ địch và giành chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Hoàn thành Trial để thêm Core Echo vào tay.</t>
+          <t>Hoàn thành Thử Thách để thêm Bản Sao Lõi vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Hoàn thành Trial để thêm Core Echo vào tay.</t>
+          <t>Hoàn thành Thử Thách để thêm Bản Sao Lõi vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Hoàn thành Trial để thêm Core Echo vào tay.</t>
+          <t>Hoàn thành Thử Thách để thêm Bản Sao Lõi vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Echoes trong Vùng Triển khai cũng có thể được Tái Cấu trúc.</t>
+          <t>Echo trong Deployment Zone cũng có thể được Tái cấu trúc.</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Echoes trong Vùng Triển khai cũng có thể được Tái Cấu trúc.</t>
+          <t>Echo trong Deployment Zone cũng có thể được Tái cấu trúc.</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Echoes trong Vùng Triển khai cũng có thể được Tái Cấu trúc.</t>
+          <t>Echo trong Deployment Zone cũng có thể được Tái cấu trúc.</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Bạn có 3 Năng Lượng. Bạn có thể kéo Chop Chop: Headless vào Khu Vực Biến Đổi và sử dụng Kỹ Năng Biến Đổi của nó.</t>
+          <t>Bạn có 3 Năng Lượng. Kéo Chop Chop: Headless vào Khu Vực Biến Đổi và sử dụng Kỹ Năng Biến Đổi của nó.</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bạn có 3 Năng Lượng. Bạn có thể kéo Chop Chop: Headless vào Khu Vực Biến Đổi và sử dụng Kỹ Năng Biến Đổi của nó.</t>
+          <t>Bạn có 3 Năng Lượng. Kéo Chop Chop: Headless vào Khu Vực Biến Đổi và sử dụng Kỹ Năng Biến Đổi của nó.</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Bạn có 3 Năng Lượng. Bạn có thể kéo Chop Chop: Headless vào Khu Vực Biến Đổi và sử dụng Kỹ Năng Biến Đổi của nó.</t>
+          <t>Bạn có 3 Năng Lượng. Kéo Chop Chop: Headless vào Khu Vực Biến Đổi và sử dụng Kỹ Năng Biến Đổi của nó.</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Triệu hồi Fusion Warrior bằng Kỹ Năng Special.</t>
+          <t>Triệu hồi Chiến Binh Fusion với Kỹ Năng Đặc Biệt.</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>{0} Triệu hồi Fusion Warrior bằng Kỹ Năng Special</t>
+          <t>Triển khai Chiến Binh Fusion có Kỹ Năng Đặc Biệt.</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Triệu hồi Fusion Warrior bằng Kỹ Năng Special.</t>
+          <t>Triệu hồi Chiến Binh Fusion với Kỹ Năng Đặc Biệt.</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{0} Dùng Orchestration để thay đổi trạng thái của các vật thể gần đó.</t>
+          <t>Sử dụng Orchestration để thay đổi trạng thái của các vật thể gần đó.</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Dùng Orchestration để thay đổi trạng thái của các vật thể gần đó.</t>
+          <t>Dùng Orchestration để thay đổi trạng thái vật thể xung quanh</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng.</t>
+          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng của chúng.</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng.</t>
+          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng của chúng.</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng.</t>
+          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng của chúng.</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=press Gamepad=press} để quỳ một gối cầu nguyện.</t>
+          <t>Nhấn {0} để quỳ một gối cầu nguyện</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để quỳ một gối cầu nguyện.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để quỳ một gối cầu nguyện.</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=press Gamepad=press} để chắp tay cầu nguyện.</t>
+          <t>Nhấn {0} để chắp tay cầu nguyện</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để chắp tay cầu nguyện.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để chắp tay cầu nguyện.</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=press Gamepad=press} để giơ tay cầu nguyện.</t>
+          <t>Nhấn {0} {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để giơ tay cầu nguyện.</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} để giơ tay cầu nguyện.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để giơ tay lên cầu nguyện.</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chỉnh sửa Quản Lý Echo.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chỉnh sửa Quản Lý Echo.</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} để chỉnh sửa Quản Lý Echo.</t>
+          <t>Nhấn {0} để chỉnh sửa Quản Lý Echo</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chỉnh sửa Quản Lý Echo.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chỉnh sửa Quản Lý Echo.</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Khởi động Quản lý tự động tại đây.</t>
+          <t>Bắt đầu Quản lý Tự động tại đây.</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Khởi động Quản lý tự động tại đây.</t>
+          <t>Bắt đầu Quản lý Tự động tại đây.</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khởi động Quản lý tự động tại đây.</t>
+          <t>Bắt đầu Quản lý Tự động tại đây.</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chỉnh sửa Tự Động Quản Lý.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chỉnh sửa Tự Động Quản Lý.</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chỉnh sửa Tự Động Quản Lý.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chỉnh sửa Tự Động Quản Lý.</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chỉnh sửa Tự Động Quản Lý.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chỉnh sửa Tự Động Quản Lý.</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Phantasma Dreamland.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Phantasma Dreamland.</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Phantasma Dreamland.</t>
+          <t>Nhấn {0} để bước vào Phantasma Dreamland</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Phantasma Dreamland.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Phantasma Dreamland.</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Kiểm tra Mục Tiêu Giai Đoạn và Môi Trường Giai Đoạn tại đây.</t>
+          <t>Xem Mục tiêu Giai đoạn và Môi trường Giai đoạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kiểm tra Mục Tiêu Giai Đoạn và Môi Trường Giai Đoạn tại đây.</t>
+          <t>Xem Mục tiêu Giai đoạn và Môi trường Giai đoạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kiểm tra Mục Tiêu Giai Đoạn và Môi Trường Giai Đoạn tại đây.</t>
+          <t>Xem Mục tiêu Giai đoạn và Môi trường Giai đoạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Chọn Phantasma Blessing trước khi bắt đầu Stage.</t>
+          <t>Chọn Phước Lành Phantasma trước khi bắt đầu Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>{0} Hãy chọn Phantasma Blessing trước khi bắt đầu Stage.</t>
+          <t>Hãy chọn Phantasma Blessing trước khi bắt đầu Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Chọn Phantasma Blessing trước khi bắt đầu Stage.</t>
+          <t>Chọn Phước Lành Phantasma trước khi bắt đầu Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Chủ động sử dụng Blessing trong Giai Đoạn để nhận buff tương ứng.</t>
+          <t>Chủ động sử dụng Phước Lành trong Giai Đoạn để nhận hiệu ứng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Chủ động sử dụng Blessing trong Giai Đoạn để nhận buff tương ứng.</t>
+          <t>Chủ động sử dụng Phước Lành trong Giai Đoạn để nhận hiệu ứng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Chủ động sử dụng Blessing trong Giai Đoạn để nhận buff tương ứng.</t>
+          <t>Chủ động sử dụng Phước Lành trong Giai Đoạn để nhận hiệu ứng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để sử dụng Blessing hiện tại.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để sử dụng Phúc Lành hiện tại.</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} để dùng Phúc Lành hiện tại.</t>
+          <t>Nhấn {0} để sử dụng Phúc Lành hiện tại</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để sử dụng Blessing hiện tại.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để sử dụng Phúc Lành hiện tại.</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Giai đoạn</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Nhấn {0} để vào Khu Vực.</t>
+          <t>Nhấn {0} để vào Giai Đoạn</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để vào Giai đoạn</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để vào Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Bạn phải đạt được mục tiêu tương ứng trước khi kết thúc mỗi Giai Đoạn.</t>
+          <t>Cậu phải đạt được mục tiêu tương ứng trước khi kết thúc mỗi Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Bạn phải đạt được mục tiêu tương ứng trước khi kết thúc mỗi Giai Đoạn.</t>
+          <t>Cậu phải đạt được mục tiêu tương ứng trước khi kết thúc mỗi Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Bạn phải đạt được mục tiêu tương ứng trước khi kết thúc mỗi Giai Đoạn.</t>
+          <t>Cậu phải đạt được mục tiêu tương ứng trước khi kết thúc mỗi Giai Đoạn.</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Giai đoạn sẽ được hoàn tất khi không còn ngày nào.</t>
+          <t>Giai đoạn này sẽ kết thúc khi không còn ngày nào nữa.</t>
         </is>
       </c>
     </row>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Giai đoạn sẽ được hoàn tất khi không còn ngày nào.</t>
+          <t>Giai đoạn này sẽ kết thúc khi không còn ngày nào nữa.</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Giai đoạn sẽ được hoàn tất khi không còn ngày nào.</t>
+          <t>Giai đoạn này sẽ kết thúc khi không còn ngày nào nữa.</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Giai đoạn tiếp theo sẽ bắt đầu sau khi đạt mục tiêu của giai đoạn hiện tại.</t>
+          <t>Giai đoạn tiếp theo sẽ bắt đầu sau khi hoàn thành mục tiêu của giai đoạn hiện tại.</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Giai đoạn tiếp theo sẽ bắt đầu sau khi đạt mục tiêu của giai đoạn hiện tại.</t>
+          <t>Giai đoạn tiếp theo sẽ bắt đầu sau khi hoàn thành mục tiêu của giai đoạn hiện tại.</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Giai đoạn tiếp theo sẽ bắt đầu sau khi đạt mục tiêu của giai đoạn hiện tại.</t>
+          <t>Giai đoạn tiếp theo sẽ bắt đầu sau khi hoàn thành mục tiêu của giai đoạn hiện tại.</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Bạn sẽ nhận được Dreamland Coupons hàng ngày dựa trên các Echoes trên chiến trường và khả năng của chúng.</t>
+          <t>Ngươi sẽ nhận được Dreamland Coupons hàng ngày dựa trên Echoes trên chiến trường và khả năng của chúng.</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Bạn sẽ nhận được Dreamland Coupons hàng ngày dựa trên các Echoes trên chiến trường và khả năng của chúng.</t>
+          <t>Ngươi sẽ nhận được Dreamland Coupons hàng ngày dựa trên Echoes trên chiến trường và khả năng của chúng.</t>
         </is>
       </c>
     </row>
@@ -11453,7 +11453,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Bạn sẽ nhận được Dreamland Coupons hàng ngày dựa trên các Echoes trên chiến trường và khả năng của chúng.</t>
+          <t>Ngươi sẽ nhận được Dreamland Coupons hàng ngày dựa trên Echoes trên chiến trường và khả năng của chúng.</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Vị trí của Echoes trên chiến trường được làm mới hàng ngày. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem chi tiết Echoes.</t>
+          <t>Vị trí các Echo trên chiến trường được làm mới hàng ngày. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem chi tiết Echo.</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Vị trí của Echoes trên chiến trường được làm mới hàng ngày. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem chi tiết Echoes.</t>
+          <t>Vị trí các Echo trên chiến trường được làm mới hàng ngày. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem chi tiết Echo.</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Vị trí của Echoes trên chiến trường được làm mới hàng ngày. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem chi tiết Echoes.</t>
+          <t>Vị trí các Echo trên chiến trường được làm mới hàng ngày. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem chi tiết Echo.</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Kiểm tra chi tiết Echo và sản lượng Phiếu Hằng Ngày tại đây.</t>
+          <t>Kiểm tra thông tin Echo và lượng phiếu hàng ngày nhận được tại đây.</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Kiểm tra chi tiết Echo và sản lượng Phiếu Hằng Ngày tại đây.</t>
+          <t>Kiểm tra thông tin Echo và lượng phiếu hàng ngày nhận được tại đây.</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Kiểm tra chi tiết Echo và sản lượng Phiếu Hằng Ngày tại đây.</t>
+          <t>Kiểm tra thông tin Echo và lượng phiếu hàng ngày nhận được tại đây.</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để bắt đầu một ngày mới.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu một ngày mới</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=Nhấn chuột Gamepad=Nhấn} vào đây để bắt đầu ngày mới.</t>
+          <t>{0} {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để bắt đầu một ngày mới.</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để bắt đầu một ngày mới.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu một ngày mới</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn 1 Echo mỗi ngày để đặt vào chiến trường.</t>
+          <t>Mỗi ngày, cậu có thể chọn 1 Echo để đặt lên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn 1 Echo mỗi ngày để đặt vào chiến trường.</t>
+          <t>Mỗi ngày, cậu có thể chọn 1 Echo để đặt lên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn 1 Echo mỗi ngày để đặt vào chiến trường.</t>
+          <t>Mỗi ngày, cậu có thể chọn 1 Echo để đặt lên chiến trường.</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Sau một ngày làm việc, bạn đã tiến gần hơn đến mục tiêu.</t>
+          <t>Sau một ngày làm việc, cậu đã tiến gần hơn đến mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Sau một ngày làm việc, bạn đã tiến gần hơn đến mục tiêu.</t>
+          <t>Sau một ngày làm việc, cậu đã tiến gần hơn đến mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Sau một ngày làm việc, bạn đã tiến gần hơn đến mục tiêu.</t>
+          <t>Sau một ngày làm việc, cậu đã tiến gần hơn đến mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Sử dụng Blessing để nhận thêm nhiều phần thưởng.</t>
+          <t>Hãy dùng Phước Lành của cậu để nhận thêm nhiều phần thưởng hơn.</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>{0} Sử dụng Blessing để nhận thêm phần thưởng.</t>
+          <t>Hãy sử dụng Phúc Lành của ngươi để nhận thêm nhiều phần thưởng hơn.</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Sử dụng Blessing để nhận thêm nhiều phần thưởng.</t>
+          <t>Hãy dùng Phước Lành của cậu để nhận thêm nhiều phần thưởng hơn.</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Blessing của bạn có giới hạn sử dụng. Hãy dùng vào thời điểm thích hợp.</t>
+          <t>Phước Lành của ngươi có giới hạn sử dụng. Hãy dùng vào thời điểm thích hợp.</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Blessing của bạn có giới hạn sử dụng. Hãy dùng vào thời điểm thích hợp.</t>
+          <t>Phước Lành của ngươi có giới hạn sử dụng. Hãy dùng vào thời điểm thích hợp.</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Blessing của bạn có giới hạn sử dụng. Hãy dùng vào thời điểm thích hợp.</t>
+          <t>Phước Lành của ngươi có giới hạn sử dụng. Hãy dùng vào thời điểm thích hợp.</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13078,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Bạn hiện có hơn 20 Echoes. Một số Echoes trên chiến trường sẽ bị tắt ngẫu nhiên.</t>
+          <t>Bạn đang có hơn 20 Echo. Một số Echo trên chiến trường sẽ bị tắt ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Bạn hiện có hơn 20 Echoes. Một số Echoes trên chiến trường sẽ bị tắt ngẫu nhiên.</t>
+          <t>Bạn đang có hơn 20 Echo. Một số Echo trên chiến trường sẽ bị tắt ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Bạn hiện có hơn 20 Echoes. Một số Echoes trên chiến trường sẽ bị tắt ngẫu nhiên.</t>
+          <t>Bạn đang có hơn 20 Echo. Một số Echo trên chiến trường sẽ bị tắt ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -13273,7 +13273,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Các Echoes bạn sở hữu được hiển thị tại đây.</t>
+          <t>Các Tacet Discord mà bạn sở hữu sẽ được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>{0} Các Echoes bạn sở hữu được hiển thị tại đây.</t>
+          <t>{0} Những Tacet Discord mà cậu sở hữu sẽ hiển thị ở đây.</t>
         </is>
       </c>
     </row>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Các Echoes bạn sở hữu được hiển thị tại đây.</t>
+          <t>Các Tacet Discord mà bạn sở hữu sẽ được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Dream Boon Giấc Mơ của bạn có thể được tăng cường.</t>
+          <t>Ước Nguyện Giấc Mơ của cậu có thể được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Dream Boon Giấc Mơ của bạn có thể được tăng cường.</t>
+          <t>Ước Nguyện Giấc Mơ của cậu có thể được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Dream Boon Giấc Mơ của bạn có thể được tăng cường.</t>
+          <t>Ước Nguyện Giấc Mơ của cậu có thể được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng cường Giấc Mơ Ban Phước tại đây.</t>
+          <t>Bạn có thể nâng cấp Phước Lành Giấc Mơ tại đây.</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng cường Giấc Mơ Ban Phước tại đây.</t>
+          <t>Bạn có thể nâng cấp Phước Lành Giấc Mơ tại đây.</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng cường Giấc Mơ Ban Phước tại đây.</t>
+          <t>Bạn có thể nâng cấp Phước Lành Giấc Mơ tại đây.</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
+          <t>Những lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
+          <t>Những lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
+          <t>Những lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
+          <t>Những lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
+          <t>Những lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
+          <t>Những lựa chọn khác nhau sẽ thay đổi giá trị chỉ số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -14443,7 +14443,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Nhớ duy trì cân bằng chỉ số. Câu chuyện sẽ kết thúc nếu một chỉ số giảm về 0.</t>
+          <t>Nhớ duy trì cân bằng chỉ số. Câu chuyện sẽ kết thúc nếu một chỉ số tụt về không đấy.</t>
         </is>
       </c>
     </row>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Nhớ duy trì cân bằng chỉ số. Câu chuyện sẽ kết thúc nếu một chỉ số giảm về 0.</t>
+          <t>Nhớ duy trì cân bằng chỉ số. Câu chuyện sẽ kết thúc nếu một chỉ số tụt về không đấy.</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Nhớ duy trì cân bằng chỉ số. Câu chuyện sẽ kết thúc nếu một chỉ số giảm về 0.</t>
+          <t>Nhớ duy trì cân bằng chỉ số. Câu chuyện sẽ kết thúc nếu một chỉ số tụt về không đấy.</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Echoes Managementes đã bật. Echoes nhận được sẽ tự động phân loại theo loại.</t>
+          <t>Đã Bật Quản Lý Tiếng Vọng. Các Tiếng Vọng Nhận Được Sẽ Tự Động Phân Loại Theo Chủng Loại.</t>
         </is>
       </c>
     </row>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Echoes Managementes đã bật. Echoes nhận được sẽ tự động phân loại theo loại.</t>
+          <t>Đã Bật Quản Lý Tiếng Vọng. Các Tiếng Vọng Nhận Được Sẽ Tự Động Phân Loại Theo Chủng Loại.</t>
         </is>
       </c>
     </row>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Echoes Managementes đã bật. Echoes nhận được sẽ tự động phân loại theo loại.</t>
+          <t>Đã Bật Quản Lý Tiếng Vọng. Các Tiếng Vọng Nhận Được Sẽ Tự Động Phân Loại Theo Chủng Loại.</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để nhập Cài đặt mặc định.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nhập cài đặt mặc định.</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} để nhập Preset mặc định.</t>
+          <t>Nhấn {0} để nhập cài đặt mặc định</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để nhập Cài đặt mặc định.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để nhập cài đặt mặc định.</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bạn có thể tiếp tục sử dụng Echoes hiện tại trong Chế độ Vô hạn.</t>
+          <t>Bạn có thể tiếp tục sử dụng Echo hiện tại trong Chế Độ Vô Tận.</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Bạn có thể tiếp tục sử dụng Echoes hiện tại trong Chế độ Vô hạn.</t>
+          <t>Bạn có thể tiếp tục sử dụng Echo hiện tại trong Chế Độ Vô Tận.</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Bạn có thể tiếp tục sử dụng Echoes hiện tại trong Chế độ Vô hạn.</t>
+          <t>Bạn có thể tiếp tục sử dụng Echo hiện tại trong Chế Độ Vô Tận.</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Echoes Dreamborne mạnh hơn Echoes thông thường.</t>
+          <t>Tiếng Vọng Giấc Mơ mạnh mẽ hơn Tiếng Vọng thông thường.</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Echoes Dreamborne mạnh hơn Echoes thông thường.</t>
+          <t>Tiếng Vọng Giấc Mơ mạnh mẽ hơn Tiếng Vọng thông thường.</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Echoes Dreamborne mạnh hơn Echoes thông thường.</t>
+          <t>Tiếng Vọng Giấc Mơ mạnh mẽ hơn Tiếng Vọng thông thường.</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Phản hồi dựa trên các chỉnh sửa của bạn.</t>
+          <t>Phản hồi sẽ dựa trên những chỉnh sửa của cậu.</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Phản hồi dựa trên các chỉnh sửa của bạn.</t>
+          <t>Phản hồi sẽ dựa trên những chỉnh sửa của cậu.</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Phản hồi dựa trên các chỉnh sửa của bạn.</t>
+          <t>Phản hồi sẽ dựa trên những chỉnh sửa của cậu.</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để vào cảnh.</t>
+          <t>Nhấn vào đây để vào cảnh.</t>
         </is>
       </c>
     </row>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để vào cảnh.</t>
+          <t>Nhấn vào đây để vào cảnh.</t>
         </is>
       </c>
     </row>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để vào cảnh.</t>
+          <t>Nhấn vào đây để vào cảnh.</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Sử dụng Tiện Ích: Zoom Camera để chụp ảnh bất kỳ lỗi nào trong cảnh.</t>
+          <t>Dùng Tiện Ích: Máy Ảnh Zoom để chụp ảnh bất kỳ con bọ nào xuất hiện trong cảnh.</t>
         </is>
       </c>
     </row>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem các Duelist đỉnh cao tại khu vực Lahai-Roi.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem bảng xếp hạng Duelist tại Khu Vực Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>{0}{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem các Duelist tại Đỉnh Prestige vùng Lahai-Roi.</t>
+          <t>Nhấn {0}{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Cao Thủ Vinh Dự tại khu vực Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem các Duelist đỉnh cao tại khu vực Lahai-Roi.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem bảng xếp hạng Duelist tại Khu Vực Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Chọn một Duelist để thách đấu</t>
+          <t>Chọn một Đấu Thủ để thách đấu</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>{0}Chọn một Đối Thủ để thách đấu</t>
+          <t>Chọn một Duelist để thách đấu</t>
         </is>
       </c>
     </row>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Chọn một Duelist để thách đấu</t>
+          <t>Chọn một Đấu Thủ để thách đấu</t>
         </is>
       </c>
     </row>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Bạn có thể Dịch Chuyển Nhanh đến vị trí của Duelist và bắt đầu đấu.</t>
+          <t>Cậu có thể Dịch Chuyển Nhanh đến vị trí của Đấu Thủ và bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Bạn có thể Dịch Chuyển Nhanh đến vị trí của Duelist và bắt đầu đấu.</t>
+          <t>Cậu có thể Dịch Chuyển Nhanh đến vị trí của Đấu Thủ và bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Bạn có thể Dịch Chuyển Nhanh đến vị trí của Duelist và bắt đầu đấu.</t>
+          <t>Cậu có thể Dịch Chuyển Nhanh đến vị trí của Đấu Thủ và bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -16653,7 +16653,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Chức năng xây dựng Bộ Hồi đã mở khóa. Bạn có thể chỉnh sửa bộ hồi tại đây.</t>
+          <t>Đã mở khóa tạo bộ bài. Bạn có thể chỉnh sửa bộ bài tại đây.</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>{0}Xây dựng Bộ Hồi Âm đã mở khóa. Bạn có thể chỉnh sửa bộ của mình tại đây.</t>
+          <t>Chức năng xây dựng bộ bài đã mở. Bạn có thể chỉnh sửa bộ bài của mình tại đây.</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Chức năng xây dựng Bộ Hồi đã mở khóa. Bạn có thể chỉnh sửa bộ hồi tại đây.</t>
+          <t>Đã mở khóa tạo bộ bài. Bạn có thể chỉnh sửa bộ bài tại đây.</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Một bộ bài phải bao gồm thẻ Domain.</t>
+          <t>Bộ bài phải bao gồm một thẻ Domain.</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>{0}Bộ bài phải bao gồm thẻ Domain.</t>
+          <t>Bộ bài phải bao gồm một thẻ Lĩnh Vực.</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Một bộ bài phải bao gồm thẻ Domain.</t>
+          <t>Bộ bài phải bao gồm một thẻ Domain.</t>
         </is>
       </c>
     </row>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Hiệu ứng &lt;color=#8c7e51&gt;Đặc biệt&lt;/color&gt; của Domain chỉ được kích hoạt khi đáp ứng yêu cầu xây dựng bộ bài nhất định</t>
+          <t>&lt;color=#8c7e51&gt;Hiệu ứng đặc biệt&lt;/color&gt; của Tổ Tacet chỉ kích hoạt khi bộ bài đáp ứng yêu cầu xây dựng nhất định.</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>{0}Hiệu ứng &lt;color=#8c7e51&gt;Special&lt;/color&gt; của Domain chỉ được kích hoạt khi đáp ứng yêu cầu xây dựng bộ bài nhất định.</t>
+          <t>{0}Hiệu ứng đặc biệt của &lt;color=#8c7e51&gt;Tổ Tacet&lt;/color&gt; chỉ được kích hoạt khi đáp ứng yêu cầu xây dựng bộ bài nhất định.</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Hiệu ứng &lt;color=#8c7e51&gt;Đặc biệt&lt;/color&gt; của Domain chỉ được kích hoạt khi đáp ứng yêu cầu xây dựng bộ bài nhất định</t>
+          <t>&lt;color=#8c7e51&gt;Hiệu ứng đặc biệt&lt;/color&gt; của Tổ Tacet chỉ kích hoạt khi bộ bài đáp ứng yêu cầu xây dựng nhất định.</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Bạn phải đáp ứng yêu cầu xây dựng bộ bài để sử dụng trong trận đấu.</t>
+          <t>Cậu phải đáp ứng yêu cầu xây dựng bộ bài để sử dụng nó trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>{0}Bạn phải đáp ứng yêu cầu xây dựng bộ bài để sử dụng trong trận đấu.</t>
+          <t>{0}cần đáp ứng yêu cầu xây dựng bộ bài mới có thể sử dụng nó trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Bạn phải đáp ứng yêu cầu xây dựng bộ bài để sử dụng trong trận đấu.</t>
+          <t>Cậu phải đáp ứng yêu cầu xây dựng bộ bài để sử dụng nó trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} một lá bài trong bộ bài của bạn để loại bỏ nó.</t>
+          <t>Nhấn vào thẻ trong bộ bài để loại bỏ nó.</t>
         </is>
       </c>
     </row>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>{0}{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào thẻ trong bộ bài để loại bỏ.</t>
+          <t>{0} vào thẻ bài trong Bộ bài của cậu để loại bỏ nó.</t>
         </is>
       </c>
     </row>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} một lá bài trong bộ bài của bạn để loại bỏ nó.</t>
+          <t>Nhấn vào thẻ trong bộ bài để loại bỏ nó.</t>
         </is>
       </c>
     </row>
@@ -17628,7 +17628,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Bạn đã sở hữu tất cả thẻ cần thiết cho bộ bài dựng sẵn này.</t>
+          <t>Bạn đã sở hữu đủ các lá bài cần thiết cho bộ bài dựng sẵn này.</t>
         </is>
       </c>
     </row>
@@ -17693,7 +17693,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Bạn đã sở hữu tất cả thẻ cần thiết cho bộ bài dựng sẵn này.</t>
+          <t>Bạn đã sở hữu đủ các lá bài cần thiết cho bộ bài dựng sẵn này.</t>
         </is>
       </c>
     </row>
@@ -17758,7 +17758,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Bạn đã sở hữu tất cả thẻ cần thiết cho bộ bài dựng sẵn này.</t>
+          <t>Bạn đã sở hữu đủ các lá bài cần thiết cho bộ bài dựng sẵn này.</t>
         </is>
       </c>
     </row>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Bạn có thể mở khóa thẻ mới bằng Prestige Point: Lahai-Roi. Tiến hành mở khóa thẻ mới.</t>
+          <t>Giờ cậu có thể mở khóa thẻ mới bằng Điểm Uy Tín: Lahai-Roi. Tiến hành mở khóa thẻ mới nào.</t>
         </is>
       </c>
     </row>
@@ -17888,7 +17888,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>{0}Bạn có thể mở khóa thẻ mới bằng Prestige Point: Lahai-Roi. Tiến hành mở khóa thẻ mới.</t>
+          <t>Giờ {0}có thể mở khóa thẻ mới bằng Điểm Uy Tín: Lahai-Roi. Tiến hành mở khóa thẻ mới nào.</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Bạn có thể mở khóa thẻ mới bằng Prestige Point: Lahai-Roi. Tiến hành mở khóa thẻ mới.</t>
+          <t>Giờ cậu có thể mở khóa thẻ mới bằng Điểm Uy Tín: Lahai-Roi. Tiến hành mở khóa thẻ mới nào.</t>
         </is>
       </c>
     </row>
@@ -18018,7 +18018,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để truy cập trang xây dựng bộ bài.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào trang xây dựng bộ bài.</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để truy cập trang xây dựng bộ bài.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào trang xây dựng bộ bài.</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để truy cập trang xây dựng bộ bài.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào trang xây dựng bộ bài.</t>
         </is>
       </c>
     </row>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để hiển thị/ẩn các thẻ bạn không sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để ẩn/hiện các thẻ bạn chưa sở hữu</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>{0}{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để hiển thị/ẩn các thẻ bạn không sở hữu.</t>
+          <t>{0} vào đây để hiển thị/ẩn các thẻ bài cậu chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để hiển thị/ẩn các thẻ bạn không sở hữu.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để ẩn/hiện các thẻ bạn chưa sở hữu</t>
         </is>
       </c>
     </row>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Dùng Prestige Point: Lahai-Roi tại đây để mở khóa các thẻ bạn chưa sở hữu.</t>
+          <t>Dùng Điểm Uy Tín: Lahai-Roi tại đây để mở khóa các thẻ bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Dùng Prestige Point: Lahai-Roi tại đây để mở khóa các thẻ bạn chưa sở hữu.</t>
+          <t>Dùng Điểm Uy Tín: Lahai-Roi tại đây để mở khóa các thẻ bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Dùng Prestige Point: Lahai-Roi tại đây để mở khóa các thẻ bạn chưa sở hữu.</t>
+          <t>Dùng Điểm Uy Tín: Lahai-Roi tại đây để mở khóa các thẻ bạn chưa sở hữu.</t>
         </is>
       </c>
     </row>
@@ -18603,7 +18603,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} Áp dụng Bộ Dàn Đề xuất và dùng bộ đề khuyến nghị để đấu.</t>
+          <t>Nhấn Suggested Deck để áp dụng và sử dụng bộ bài đề xuất trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -18668,7 +18668,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>{0}{Cus:Ipt,Touch=tap PC=click Gamepad=press} để áp dụng Bộ Thẻ Gợi Ý và sử dụng bộ thẻ đề xuất trong trận đấu.</t>
+          <t>{0} để áp dụng và sử dụng Bộ bài gợi ý trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} Áp dụng Bộ Dàn Đề xuất và dùng bộ đề khuyến nghị để đấu.</t>
+          <t>Nhấn Suggested Deck để áp dụng và sử dụng bộ bài đề xuất trong trận đấu.</t>
         </is>
       </c>
     </row>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các Duelist Vinh Quang ở các khu vực khác nhau.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem danh sách Duelists tại Peaks of Prestige ở các khu vực khác nhau.</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18863,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem Danh sách Duelist Vinh Quang ở các khu vực khác nhau.</t>
+          <t>{0} {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem danh sách Duelist Đỉnh Cao ở các khu vực khác nhau.</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các Duelist Vinh Quang ở các khu vực khác nhau.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem danh sách Duelists tại Peaks of Prestige ở các khu vực khác nhau.</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Chọn đội cho Bài Kiểm Tra Tinh Thông Combat.</t>
+          <t>Chọn đội hình cho Bài Kiểm Tra Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Chọn đội cho Bài Kiểm Tra Tinh Thông Combat.</t>
+          <t>Chọn đội hình cho Bài Kiểm Tra Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -19123,7 +19123,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Chọn đội cho Bài Kiểm Tra Tinh Thông Combat.</t>
+          <t>Chọn đội hình cho Bài Kiểm Tra Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các hiệu ứng trạng thái có thể xảy ra.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các hiệu ứng trạng thái có thể gặp.</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các hiệu ứng trạng thái có thể xảy ra.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các hiệu ứng trạng thái có thể gặp.</t>
         </is>
       </c>
     </row>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các hiệu ứng trạng thái có thể xảy ra.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các hiệu ứng trạng thái có thể gặp.</t>
         </is>
       </c>
     </row>
@@ -19383,7 +19383,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Sử dụng Tiện Ích: Zoom Camera để chụp ảnh bất kỳ lỗi nào trong cảnh.</t>
+          <t>Dùng Tiện Ích: Máy Ảnh Zoom để chụp ảnh bất kỳ con bọ nào xuất hiện trong cảnh.</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Cảm ơn bạn đã tham gia Tidal Defense Simulator. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để vào sân đấu.</t>
+          <t>Cảm ơn bạn đã tham gia Mô Phỏng Phòng Thủ Thủy Triều. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào trận.</t>
         </is>
       </c>
     </row>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Cảm ơn bạn đã tham gia Tidal Defense Simulator. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để vào sân đấu.</t>
+          <t>Cảm ơn bạn đã tham gia Mô Phỏng Phòng Thủ Thủy Triều. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào trận.</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Cảm ơn bạn đã tham gia Tidal Defense Simulator. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để vào sân đấu.</t>
+          <t>Cảm ơn bạn đã tham gia Mô Phỏng Phòng Thủ Thủy Triều. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để vào trận.</t>
         </is>
       </c>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Chi tiết giai đoạn và bản đồ được hiển thị tại đây.</t>
+          <t>Thông tin chi tiết và bản đồ sân khấu hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Chi tiết giai đoạn và bản đồ được hiển thị tại đây.</t>
+          <t>Thông tin chi tiết và bản đồ sân khấu hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Chi tiết giai đoạn và bản đồ được hiển thị tại đây.</t>
+          <t>Thông tin chi tiết và bản đồ sân khấu hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Hoàn thành mục tiêu thử thách để nhận Ngôi Sao Đánh Giá.</t>
+          <t>Hoàn thành mục tiêu thử thách để kiếm Ngôi Sao Xếp Hạng.</t>
         </is>
       </c>
     </row>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hoàn thành mục tiêu thử thách để nhận Ngôi Sao Đánh Giá.</t>
+          <t>Hoàn thành mục tiêu thử thách để kiếm Ngôi Sao Xếp Hạng.</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hoàn thành mục tiêu thử thách để nhận Ngôi Sao Đánh Giá.</t>
+          <t>Hoàn thành mục tiêu thử thách để kiếm Ngôi Sao Xếp Hạng.</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để bắt đầu mô phỏng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu mô phỏng.</t>
         </is>
       </c>
     </row>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để bắt đầu mô phỏng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu mô phỏng.</t>
         </is>
       </c>
     </row>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để bắt đầu mô phỏng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu mô phỏng.</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} để chọn Combat Machines triển khai chống lại Tacet Discord.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để chọn Máy Chiến Đấu triển khai chống lại Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} để chọn Combat Machines triển khai chống lại Tacet Discord.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để chọn Máy Chiến Đấu triển khai chống lại Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -20358,7 +20358,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} để chọn Combat Machines triển khai chống lại Tacet Discords.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để chọn Máy Chiến Đấu triển khai chống lại Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Số Sim Credits hiện tại và Combat Machine đã triển khai của bạn được hiển thị tại đây.</t>
+          <t>Số Sim Credit và Combat Machine đang triển khai của cậu được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Số Sim Credits hiện tại và Combat Machine đã triển khai của bạn được hiển thị tại đây.</t>
+          <t>Số Sim Credit và Combat Machine đang triển khai của cậu được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Số Sim Credits hiện tại và Combat Machine đã triển khai của bạn được hiển thị tại đây.</t>
+          <t>Số Sim Credit và Combat Machine đang triển khai của cậu được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -20813,7 +20813,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ngăn kẻ địch tiếp cận Energy Matrix. Nếu Độ Bền giảm về 0, thử thách sẽ thất bại.</t>
+          <t>Ngăn địch tiếp cận Ma Trận Năng Lượng. Nếu Độ Bền của nó giảm về 0, thử thách sẽ thất bại.</t>
         </is>
       </c>
     </row>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Ngăn kẻ địch tiếp cận Energy Matrix. Nếu Độ Bền giảm về 0, thử thách sẽ thất bại.</t>
+          <t>Ngăn địch tiếp cận Ma Trận Năng Lượng. Nếu Độ Bền của nó giảm về 0, thử thách sẽ thất bại.</t>
         </is>
       </c>
     </row>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Ngăn kẻ địch tiếp cận Energy Matrix. Nếu Độ Bền giảm về 0, thử thách sẽ thất bại.</t>
+          <t>Ngăn địch tiếp cận Ma Trận Năng Lượng. Nếu Độ Bền của nó giảm về 0, thử thách sẽ thất bại.</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} nút &lt;color=#ffd12f&gt;Bắn&lt;/color&gt; và &lt;color=#ffd12f&gt;Speed Shooter&lt;/color&gt; sẽ &lt;color=#ffd12f&gt;tự động ngắm&lt;/color&gt; và tấn công mục tiêu gần đó.</t>
+          <t>Nhấn nút &lt;color=#ffd12f&gt;Tấn Công&lt;/color&gt; và &lt;color=#ffd12f&gt;Speed Shooter&lt;/color&gt; để tự động &lt;color=#ffd12f&gt;khóa mục tiêu&lt;/color&gt; và tấn công kẻ địch gần đó.</t>
         </is>
       </c>
     </row>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để điều chỉnh Combat Machines trước khi bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để điều chỉnh Máy Chiến Đấu trước khi bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -21268,7 +21268,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để điều chỉnh Combat Machines trước khi bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để điều chỉnh Máy Chiến Đấu trước khi bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Bạn có thể điều chỉnh Combat Machines trước khi bắt đầu thử thách.</t>
+          <t>Cậu có thể điều chỉnh Máy Chiến Đấu trước khi bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Một số giai đoạn yêu cầu trang bị Combat Machine cụ thể trước khi bắt đầu.</t>
+          <t>Một số màn chơi yêu cầu phải trang bị Máy Chiến Đấu cụ thể trước khi bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Một số giai đoạn yêu cầu trang bị Combat Machine cụ thể trước khi bắt đầu.</t>
+          <t>Một số màn chơi yêu cầu phải trang bị Máy Chiến Đấu cụ thể trước khi bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Một số giai đoạn yêu cầu trang bị Combat Machine cụ thể trước khi bắt đầu.</t>
+          <t>Một số màn chơi yêu cầu phải trang bị Máy Chiến Đấu cụ thể trước khi bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -21593,7 +21593,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Ngôi Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
+          <t>Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
         </is>
       </c>
     </row>
@@ -21658,7 +21658,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>{0} Rating Stars có thể dùng để mở khóa Overwatch Protocols.</t>
+          <t>{0} Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
         </is>
       </c>
     </row>
@@ -21723,7 +21723,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Ngôi Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
+          <t>Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Dùng Sim Ingot để cải thiện hiệu suất của Combat Machines và vũ khí của KU-Roro.</t>
+          <t>Dùng Thỏi Sim để nâng cấp hiệu suất của Máy Chiến Đấu và vũ khí của KU-Roro.</t>
         </is>
       </c>
     </row>
@@ -22048,7 +22048,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Dùng {0} để sử dụng Sim Ingot nhằm cải thiện hiệu suất của Combat Machines và vũ khí của KU-Roro.</t>
+          <t>Nhấn {0} để dùng Thỏi Sim cải thiện hiệu suất Máy Chiến Đấu và vũ khí của KU-Roro</t>
         </is>
       </c>
     </row>
@@ -22113,7 +22113,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Dùng Sim Ingot để cải thiện hiệu suất của Combat Machines và vũ khí của KU-Roro.</t>
+          <t>Dùng Thỏi Sim để nâng cấp hiệu suất của Máy Chiến Đấu và vũ khí của KU-Roro.</t>
         </is>
       </c>
     </row>
@@ -22178,7 +22178,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển đổi Optional Modules bất cứ lúc nào.</t>
+          <t>Bạn có thể chuyển đổi Mô-đun Tùy Chọn bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -22243,7 +22243,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển đổi Optional Modules bất cứ lúc nào.</t>
+          <t>Bạn có thể chuyển đổi Mô-đun Tùy Chọn bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển đổi Optional Modules bất cứ lúc nào.</t>
+          <t>Bạn có thể chuyển đổi Mô-đun Tùy Chọn bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Mở khóa Mô-đun Tùy Chọn ở Lv. 3 để tăng cường Máy Chiến Đấu.</t>
+          <t>Mở khóa Mô-đun Tùy Chọn cấp 3 để tăng cường Máy Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -22438,7 +22438,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Mở khóa Mô-đun Tùy Chọn ở Lv. 3 để tăng cường Máy Chiến Đấu.</t>
+          <t>Mở khóa Mô-đun Tùy Chọn cấp 3 để tăng cường Máy Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Mở khóa Mô-đun Tùy Chọn ở Lv. 3 để tăng cường Máy Chiến Đấu.</t>
+          <t>Mở khóa Mô-đun Tùy Chọn cấp 3 để tăng cường Máy Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Các cơ chế bổ sung có thể xuất hiện ở các giai đoạn khó hơn.</t>
+          <t>Các cơ chế bổ sung có thể xuất hiện ở những màn khó hơn.</t>
         </is>
       </c>
     </row>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Các cơ chế bổ sung có thể xuất hiện ở các giai đoạn khó hơn.</t>
+          <t>Các cơ chế bổ sung có thể xuất hiện ở những màn khó hơn.</t>
         </is>
       </c>
     </row>
@@ -22698,7 +22698,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Các cơ chế bổ sung có thể xuất hiện ở các giai đoạn khó hơn.</t>
+          <t>Các cơ chế bổ sung có thể xuất hiện ở những màn khó hơn.</t>
         </is>
       </c>
     </row>
@@ -22763,7 +22763,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Bạn có thể điều chỉnh độ khó tại đây.</t>
+          <t>Cậu có thể điều chỉnh độ khó ở đây.</t>
         </is>
       </c>
     </row>
@@ -22828,7 +22828,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Bạn có thể điều chỉnh độ khó tại đây.</t>
+          <t>Cậu có thể điều chỉnh độ khó ở đây.</t>
         </is>
       </c>
     </row>
@@ -22893,7 +22893,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Bạn có thể điều chỉnh độ khó tại đây.</t>
+          <t>Cậu có thể điều chỉnh độ khó ở đây.</t>
         </is>
       </c>
     </row>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tactics tăng cường buff cho Combat Machines.</t>
+          <t>Chiến thuật tăng cường hiệu ứng cho Máy Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -23023,7 +23023,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Tactics tăng cường buff cho Combat Machines.</t>
+          <t>Chiến thuật tăng cường hiệu ứng cho Máy Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Tactics tăng cường buff cho Combat Machines.</t>
+          <t>Chiến thuật tăng cường hiệu ứng cho Máy Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -23153,7 +23153,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Càng sở hữu nhiều Tactics liên quan, cơ hội xuất hiện các Tactics mạnh càng cao.</t>
+          <t>Càng sở hữu nhiều Chiến Thuật liên quan, khả năng xuất hiện những Chiến Thuật mạnh mẽ càng cao.</t>
         </is>
       </c>
     </row>
@@ -23218,7 +23218,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Càng sở hữu nhiều Tactics liên quan, cơ hội xuất hiện các Tactics mạnh càng cao.</t>
+          <t>Càng sở hữu nhiều Chiến Thuật liên quan, khả năng xuất hiện những Chiến Thuật mạnh mẽ càng cao.</t>
         </is>
       </c>
     </row>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Càng sở hữu nhiều Tactics liên quan, cơ hội xuất hiện các Tactics mạnh càng cao.</t>
+          <t>Càng sở hữu nhiều Chiến Thuật liên quan, khả năng xuất hiện những Chiến Thuật mạnh mẽ càng cao.</t>
         </is>
       </c>
     </row>
@@ -23348,7 +23348,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Xem Chiến Thuật bạn hiện sở hữu tại đây.</t>
+          <t>Xem Chiến Thuật hiện có của bạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>{0} để xem Tactics hiện có của bạn.</t>
+          <t>Nhấn {0} để xem Chiến Thuật hiện có của cậu</t>
         </is>
       </c>
     </row>
@@ -23478,7 +23478,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Xem Chiến Thuật bạn hiện sở hữu tại đây.</t>
+          <t>Xem Chiến Thuật hiện có của bạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>{0} Mua vật phẩm và Chiến thuật từ KU-Money's Shop.</t>
+          <t>Mua vật phẩm và Chiến Thuật từ Cửa Hàng KU-Money.</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>{0} Mua vật phẩm và Chiến thuật từ KU-Money's Shop.</t>
+          <t>Mua vật phẩm và Chiến Thuật từ Cửa Hàng KU-Money.</t>
         </is>
       </c>
     </row>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Bạn có thể mua vật phẩm và Tactics từ Shop KU-Money.</t>
+          <t>Bạn có thể mua vật phẩm và Chiến thuật từ Cửa hàng của KU-Money.</t>
         </is>
       </c>
     </row>
@@ -23738,7 +23738,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ember tích lũy trong chiến đấu. Khi đạt 100%, bạn sẽ bước vào trạng thái Burning Waves.</t>
+          <t>Lửa Chiến tích lũy trong trận đấu. Khi đạt 100%, bạn sẽ bước vào trạng thái Sóng Lửa Cháy.</t>
         </is>
       </c>
     </row>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>{0}+{1} Ember tích lũy trong chiến đấu. Khi đạt 100%, bạn sẽ vào trạng thái Burning Waves.</t>
+          <t>{0}+{1} Lửa Âm Dương tích lũy trong chiến đấu. Khi đạt 100%, bạn sẽ bước vào trạng thái Sóng Lửa Bùng Cháy.</t>
         </is>
       </c>
     </row>
@@ -23868,7 +23868,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Ember tích lũy trong chiến đấu. Khi đạt 100%, bạn sẽ bước vào trạng thái Burning Waves.</t>
+          <t>Lửa Chiến tích lũy trong trận đấu. Khi đạt 100%, bạn sẽ bước vào trạng thái Sóng Lửa Cháy.</t>
         </is>
       </c>
     </row>
@@ -23933,7 +23933,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Chọn một Sigil. Nó sẽ tự động kích hoạt khi điều kiện được đáp ứng.</t>
+          <t>Chọn một Ấn Tượng. Nó sẽ tự động kích hoạt khi đạt điều kiện.</t>
         </is>
       </c>
     </row>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Chọn một Sigil. Nó sẽ tự động kích hoạt khi điều kiện được đáp ứng.</t>
+          <t>Chọn một Ấn Tượng. Nó sẽ tự động kích hoạt khi đạt điều kiện.</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Chọn một Sigil. Nó sẽ tự động kích hoạt khi điều kiện được đáp ứng.</t>
+          <t>Chọn một Ấn Tượng. Nó sẽ tự động kích hoạt khi đạt điều kiện.</t>
         </is>
       </c>
     </row>
@@ -24128,7 +24128,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Năng Lượng Giấc Mơ tích lũy khi Resonators tấn công.</t>
+          <t>Năng Lượng Cảnh Mộng tích lũy khi Resonator tấn công.</t>
         </is>
       </c>
     </row>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Năng Lượng Giấc Mơ tích lũy khi Resonators tấn công.</t>
+          <t>Năng Lượng Cảnh Mộng tích lũy khi Resonator tấn công.</t>
         </is>
       </c>
     </row>
@@ -24258,7 +24258,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Năng Lượng Giấc Mơ tích lũy khi Resonators tấn công.</t>
+          <t>Năng Lượng Cảnh Mộng tích lũy khi Resonator tấn công.</t>
         </is>
       </c>
     </row>
@@ -24323,7 +24323,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Kích hoạt Ấn Ký để bước vào trạng thái Divined Dream và nhận hiệu ứng tăng cường.</t>
+          <t>Kích hoạt Ấn để bước vào trạng thái Giấc Mơ Tiên Tri và nhận hiệu ứng tăng cường</t>
         </is>
       </c>
     </row>
@@ -24388,7 +24388,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>{0} + {1} Kích hoạt Sigil để bước vào trạng thái Divined Dream và nhận hiệu ứng tăng cường.</t>
+          <t>{0} + {1} Kích hoạt Ấn Tượng để bước vào trạng thái Giấc Mơ Tiên Tri và nhận hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -24453,7 +24453,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kích hoạt Ấn Ký để bước vào trạng thái Divined Dream và nhận hiệu ứng tăng cường.</t>
+          <t>Kích hoạt Ấn để bước vào trạng thái Giấc Mơ Tiên Tri và nhận hiệu ứng tăng cường</t>
         </is>
       </c>
     </row>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Ở Infinite Mode, có thể tăng tốc độ thao tác lên mức tối đa.</t>
+          <t>Trong Chế Độ Vô Tận, các thao tác có thể tăng tốc lên mức tối đa.</t>
         </is>
       </c>
     </row>
@@ -24583,7 +24583,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Ở Infinite Mode, có thể tăng tốc độ thao tác lên mức tối đa.</t>
+          <t>Trong Chế Độ Vô Tận, các thao tác có thể tăng tốc lên mức tối đa.</t>
         </is>
       </c>
     </row>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Ở Infinite Mode, có thể tăng tốc độ thao tác lên mức tối đa.</t>
+          <t>Trong Chế Độ Vô Tận, các thao tác có thể tăng tốc lên mức tối đa.</t>
         </is>
       </c>
     </row>
@@ -24713,7 +24713,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Bạn có thể tự động trang bị đội hình Combat Machine được đề xuất cho giai đoạn hiện tại.</t>
+          <t>Cậu có thể tự động trang bị đội hình Chiến Cơ được đề xuất cho giai đoạn hiện tại.</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Bạn có thể tự động trang bị đội hình Combat Machine được đề xuất cho giai đoạn hiện tại.</t>
+          <t>Cậu có thể tự động trang bị đội hình Chiến Cơ được đề xuất cho giai đoạn hiện tại.</t>
         </is>
       </c>
     </row>
@@ -24843,7 +24843,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Bạn có thể tự động trang bị đội hình Combat Machine được đề xuất cho giai đoạn hiện tại.</t>
+          <t>Cậu có thể tự động trang bị đội hình Chiến Cơ được đề xuất cho giai đoạn hiện tại.</t>
         </is>
       </c>
     </row>
@@ -24908,7 +24908,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng của Combat Machines ở các cấp độ khác nhau tại đây.</t>
+          <t>Cậu có thể xem hiệu ứng của Máy Chiến Đấu ở các cấp độ khác nhau tại đây.</t>
         </is>
       </c>
     </row>
@@ -24973,7 +24973,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Nhấn {0} để xem hiệu ứng thuộc tính của Combat Machine tại đây.</t>
+          <t>Nhấn {0} để xem hiệu ứng Thuộc Tính của Máy Chiến Đấu tại đây</t>
         </is>
       </c>
     </row>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng của Combat Machines ở các cấp độ khác nhau tại đây.</t>
+          <t>Cậu có thể xem hiệu ứng của Máy Chiến Đấu ở các cấp độ khác nhau tại đây.</t>
         </is>
       </c>
     </row>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=press Gamepad=press} để xem bản đồ và lộ trình tiến triển của Tacet Discord.</t>
+          <t>Nhấn {0} {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để xem bản đồ và lộ trình tiến công của các Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=press Gamepad=press} để xem bản đồ và lộ trình tiến triển của Tacet Discord.</t>
+          <t>Nhấn {0} {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để xem bản đồ và lộ trình tiến công của các Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -25233,7 +25233,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem bản đồ và lộ trình tiến quân của Tacet Discord.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem bản đồ và lộ trình tiến công của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -25298,7 +25298,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Ngôi Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
+          <t>Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
         </is>
       </c>
     </row>
@@ -25363,7 +25363,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Ngôi Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
+          <t>Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25428,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Ngôi Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
+          <t>Sao Đánh Giá có thể dùng để mở khóa Giao Thức Giám Sát.</t>
         </is>
       </c>
     </row>
@@ -25493,7 +25493,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Mục tiêu nguy hiểm đang đến gần. Check chi tiết đợt tấn công tại đây.</t>
+          <t>Mục tiêu nguy hiểm đang tiến đến. Kiểm tra chi tiết đợt sóng tại đây.</t>
         </is>
       </c>
     </row>
@@ -25558,7 +25558,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>{0} Mục tiêu nguy hiểm đang đến gần. Xem chi tiết đợt sóng tại đây.</t>
+          <t>Mục tiêu nguy hiểm đang đến gần. Kiểm tra chi tiết đợt sóng tại đây.</t>
         </is>
       </c>
     </row>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Bạn có thể xem chi tiết đợt sóng tại đây.</t>
+          <t>Cậu có thể kiểm tra chi tiết đợt sóng tại đây.</t>
         </is>
       </c>
     </row>
@@ -25688,7 +25688,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Mục tiêu nguy hiểm đang đến gần. Check chi tiết đợt tấn công tại đây.</t>
+          <t>Mục tiêu nguy hiểm đang tiến đến. Kiểm tra chi tiết đợt sóng tại đây.</t>
         </is>
       </c>
     </row>
@@ -25753,7 +25753,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Một số Tacet Discord có đặc tính tăng cường. Hãy cẩn thận.</t>
+          <t>Một số Tacet Discord sở hữu đặc tính tăng cường. Hãy cẩn trọng!</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Một số Tacet Discord có đặc tính tăng cường. Hãy cẩn thận.</t>
+          <t>Một số Tacet Discord sở hữu đặc tính tăng cường. Hãy cẩn trọng!</t>
         </is>
       </c>
     </row>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Một số Tacet Discord có đặc tính tăng cường. Hãy cẩn thận.</t>
+          <t>Một số Tacet Discord sở hữu đặc tính tăng cường. Hãy cẩn trọng!</t>
         </is>
       </c>
     </row>
@@ -25948,7 +25948,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Xem Chiến Thuật bạn hiện sở hữu tại đây.</t>
+          <t>Xem Chiến Thuật hiện có của bạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái Half Moon, hồi phục Forte Gauge khi trúng đòn.</t>
+          <t>Khi ở trạng thái Bán Nguyệt, hồi phục Đồng Vĩ khi tấn công trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -26078,7 +26078,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái Half Moon, hồi phục Forte Gauge khi trúng đòn.</t>
+          <t>Khi ở trạng thái Bán Nguyệt, hồi phục Đồng Vĩ khi tấn công trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -26143,7 +26143,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái Half Moon, hồi phục Forte Gauge khi trúng đòn.</t>
+          <t>Khi ở trạng thái Bán Nguyệt, hồi phục Đồng Vĩ khi tấn công trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Tấn công bằng Moonbow tiêu hao Forte Gauge, tăng Skill Amplification, phục hồi Concerto Energy và hồi máu.</t>
+          <t>Tấn công bằng Moonbow tiêu hao Forte Gauge, tăng cường Skill Amplification, hồi phục Concerto Energy và phục hồi HP.</t>
         </is>
       </c>
     </row>
@@ -26273,7 +26273,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tấn công bằng Moonbow tiêu hao Forte Gauge, tăng Skill Amplification, phục hồi Concerto Energy và hồi máu.</t>
+          <t>Tấn công bằng Moonbow tiêu hao Forte Gauge, tăng cường Skill Amplification, hồi phục Concerto Energy và phục hồi HP.</t>
         </is>
       </c>
     </row>
@@ -26338,7 +26338,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Tấn công bằng Moonbow tiêu hao Forte Gauge, tăng Skill Amplification, phục hồi Concerto Energy và hồi máu.</t>
+          <t>Tấn công bằng Moonbow tiêu hao Forte Gauge, tăng cường Skill Amplification, hồi phục Concerto Energy và phục hồi HP.</t>
         </is>
       </c>
     </row>
@@ -26403,7 +26403,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Heavy Attack: Absolute Fullness có thể sử dụng khi Concerto Energy đầy.</t>
+          <t>Đòn Heavy Attack: Absolute Fullness can be cast once Concerto Energy is full.</t>
         </is>
       </c>
     </row>
@@ -26468,7 +26468,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Heavy Attack: Absolute Fullness có thể sử dụng khi Concerto Energy đầy.</t>
+          <t>Đòn Heavy Attack: Absolute Fullness can be cast once Concerto Energy is full.</t>
         </is>
       </c>
     </row>
@@ -26533,7 +26533,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Heavy Attack: Absolute Fullness có thể sử dụng khi Concerto Energy đầy.</t>
+          <t>Đòn Heavy Attack: Absolute Fullness can be cast once Concerto Energy is full.</t>
         </is>
       </c>
     </row>
@@ -26598,7 +26598,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>{0} để &lt;color=#ffd12f&gt;Bắn&lt;/color&gt; &lt;color=#ffd12f&gt;Plasma Cannon&lt;/color&gt;. &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; nút bắn để nạp đạn.</t>
+          <t>Nhấn {0} để &lt;color=#ffd12f&gt;bắn&lt;/color&gt; &lt;color=#ffd12f&gt;Pháo Plasma Lửa&lt;/color&gt;. Giữ nút để tích năng lượng.</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>{0} để &lt;color=#ffd12f&gt;Bắn&lt;/color&gt; &lt;color=#ffd12f&gt;Plasma Cannon&lt;/color&gt;. &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; nút bắn để nạp đạn.</t>
+          <t>Nhấn {0} để &lt;color=#ffd12f&gt;bắn&lt;/color&gt; &lt;color=#ffd12f&gt;Pháo Plasma Lửa&lt;/color&gt;. Giữ nút để tích năng lượng.</t>
         </is>
       </c>
     </row>
@@ -26728,7 +26728,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} &lt;color=#ffd12f&gt;Bắn&lt;/color&gt; &lt;color=#ffd12f&gt;Plasma Cannon&lt;/color&gt;. &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; nút bắn để tích năng lượng.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} &lt;color=#ffd12f&gt;Pháo Plasma Lửa&lt;/color&gt;. &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để nạp đạn.</t>
         </is>
       </c>
     </row>
@@ -26793,7 +26793,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Nhấn {0} để kích hoạt &lt;color=#ffd12f&gt;Kích hoạt&lt;/color&gt; &lt;color=#ffd12f&gt;Trường Đẩy&lt;/color&gt;. Bạn không thể kích hoạt lại cho đến khi Cooldown kết thúc.</t>
+          <t>Nhấn {0} để &lt;color=#ffd12f&gt;kích hoạt&lt;/color&gt; &lt;color=#ffd12f&gt;Trường Đẩy Lùi&lt;/color&gt;. Không thể sử dụng lại cho đến khi Thời gian hồi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -26858,7 +26858,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nhấn {0} để kích hoạt &lt;color=#ffd12f&gt;Kích hoạt&lt;/color&gt; &lt;color=#ffd12f&gt;Trường Đẩy&lt;/color&gt;. Bạn không thể kích hoạt lại cho đến khi Cooldown kết thúc.</t>
+          <t>Nhấn {0} để &lt;color=#ffd12f&gt;kích hoạt&lt;/color&gt; &lt;color=#ffd12f&gt;Trường Đẩy Lùi&lt;/color&gt;. Không thể sử dụng lại cho đến khi Thời gian hồi kết thúc.</t>
         </is>
       </c>
     </row>
@@ -26923,7 +26923,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} &lt;color=#ffd12f&gt;Kích hoạt&lt;/color&gt; &lt;color=#ffd12f&gt;Trường Đẩy&lt;/color&gt;. Bạn không thể bắn lại cho đến khi hết Cooldown.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} &lt;color=#ffd12f&gt;Trường Đẩy Lùi&lt;/color&gt;. Cậu không thể bắn lại cho đến khi Thời gian hồi chiêu kết thúc.</t>
         </is>
       </c>
     </row>
@@ -26988,7 +26988,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>{0} Dùng Công Cụ: Bay Lượn để nhảy lên không và bắt đầu bay.</t>
+          <t>Sử dụng Utility: Flight để nhảy lên không và bắt đầu bay.</t>
         </is>
       </c>
     </row>
@@ -27053,7 +27053,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Dùng Công Cụ: Bay Lượn để bật lên không trung và bắt đầu bay.</t>
+          <t>Dùng Tiện Ích: Bay để nhảy lên không và bắt đầu bay.</t>
         </is>
       </c>
     </row>
@@ -27118,7 +27118,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Máy Combat này có thể nâng cấp lên Cấp 2 để tăng &lt;color=#8c7e51&gt;các chỉ số&lt;/color&gt; của nó.</t>
+          <t>Máy Chiến Đấu này có thể nâng cấp lên Cấp 2, giúp tăng &lt;color=#8c7e51&gt;chỉ số của nó&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Máy Combat này có thể nâng cấp lên Cấp 2 để tăng &lt;color=#8c7e51&gt;các chỉ số&lt;/color&gt; của nó.</t>
+          <t>Máy Chiến Đấu này có thể nâng cấp lên Cấp 2, giúp tăng &lt;color=#8c7e51&gt;chỉ số của nó&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Máy Combat này có thể nâng cấp lên Cấp 2 để tăng &lt;color=#8c7e51&gt;các chỉ số&lt;/color&gt; của nó.</t>
+          <t>Máy Chiến Đấu này có thể nâng cấp lên Cấp 2, giúp tăng &lt;color=#8c7e51&gt;chỉ số của nó&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27313,7 +27313,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Bạn có thể đặt lại nâng cấp và &lt;color=#8c7e51&gt;hoàn trả&lt;/color&gt; toàn bộ Sim Ingots đã tiêu hao tại đây bất cứ lúc nào.</t>
+          <t>Bạn có thể đặt lại nâng cấp và &lt;color=#8c7e51&gt;hoàn trả&lt;/color&gt; toàn bộ Sim Ingot đã tiêu hao tại đây bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -27378,7 +27378,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể reset nâng cấp và &lt;color=#8c7e51&gt;hoàn trả&lt;/color&gt; toàn bộ Sim Ingots đã tiêu hao tại đây bất cứ lúc nào.</t>
+          <t>{0} Cậu có thể đặt lại nâng cấp và &lt;color=#8c7e51&gt;hoàn trả&lt;/color&gt; toàn bộ Sim Ingot đã tiêu thụ tại đây bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -27443,7 +27443,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Bạn có thể đặt lại nâng cấp và &lt;color=#8c7e51&gt;hoàn trả&lt;/color&gt; toàn bộ Sim Ingots đã tiêu hao tại đây bất cứ lúc nào.</t>
+          <t>Bạn có thể đặt lại nâng cấp và &lt;color=#8c7e51&gt;hoàn trả&lt;/color&gt; toàn bộ Sim Ingot đã tiêu hao tại đây bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -27508,7 +27508,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Nâng cấp &lt;color=#8c7e51&gt;Cỗ Máy Combat&lt;/color&gt; lên Cấp 3 để mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt;.</t>
+          <t>Nâng cấp &lt;color=#8c7e51&gt;Cỗ Máy Chiến Đấu&lt;/color&gt; lên Cấp 3 để mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>{0} Nâng cấp &lt;color=#8c7e51&gt;Cỗ Máy Combat&lt;/color&gt; lên Cấp 3 để mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt;.</t>
+          <t>{0} Nâng cấp &lt;color=#8c7e51&gt;Cỗ Máy Chiến Đấu&lt;/color&gt; lên Cấp 3 để mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Nâng cấp &lt;color=#8c7e51&gt;Cỗ Máy Combat&lt;/color&gt; lên Cấp 3 để mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt;.</t>
+          <t>Nâng cấp &lt;color=#8c7e51&gt;Cỗ Máy Chiến Đấu&lt;/color&gt; lên Cấp 3 để mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Máy Combat này có thể nâng cấp từ Cấp 2 lên Cấp 3.</t>
+          <t>Máy Chiến Đấu này có thể nâng cấp từ Cấp 2 lên Cấp 3.</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Máy Combat này có thể nâng cấp từ Cấp 2 lên Cấp 3.</t>
+          <t>Máy Chiến Đấu này có thể nâng cấp từ Cấp 2 lên Cấp 3.</t>
         </is>
       </c>
     </row>
@@ -27833,7 +27833,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Máy Combat này có thể nâng cấp từ Cấp 2 lên Cấp 3.</t>
+          <t>Máy Chiến Đấu này có thể nâng cấp từ Cấp 2 lên Cấp 3.</t>
         </is>
       </c>
     </row>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đạt Cấp 3 sẽ mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt; của Combat Cơ.</t>
+          <t>Đạt Cấp 3 sẽ mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt; của Cỗ Máy Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Đạt Cấp 3 sẽ mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt; của Combat Cơ.</t>
+          <t>Đạt Cấp 3 sẽ mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt; của Cỗ Máy Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Đạt Cấp 3 sẽ mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt; của Combat Cơ.</t>
+          <t>Đạt Cấp 3 sẽ mở khóa &lt;color=#8c7e51&gt;Mô-đun Tùy Chọn&lt;/color&gt; của Cỗ Máy Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -28093,7 +28093,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} Journey Log để xem lịch sử nhiệm vụ.</t>
+          <t>Nhấn Journey Log để xem lịch sử nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -28158,7 +28158,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nhấn {0} để mở Journey Log và xem lịch sử nhiệm vụ</t>
+          <t>Mở Nhật Ký Hành Trình để xem lịch sử nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} Journey Log để xem lịch sử nhiệm vụ</t>
+          <t>Nhấn Journey Log để xem lịch sử nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Đã mở khóa giao diện Terminal mới. Xem ngay nào!</t>
+          <t>Giao diện Thiết bị đầu cuối mới đã mở khóa. Xem ngay nào!</t>
         </is>
       </c>
     </row>
@@ -28353,7 +28353,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>{0} ngoại hình Điểm Kết Nối mới đã mở khóa. Xem ngay!</t>
+          <t>Đã mở khóa giao diện Thiết bị đầu cuối mới. {0} hãy xem ngay nào!</t>
         </is>
       </c>
     </row>
@@ -28418,7 +28418,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Đã mở khóa giao diện Terminal mới. Xem ngay nào!</t>
+          <t>Giao diện Thiết bị đầu cuối mới đã mở khóa. Xem ngay nào!</t>
         </is>
       </c>
     </row>
@@ -28483,7 +28483,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi ngoại hình Terminal của Rover</t>
+          <t>Cậu có thể thay đổi diện mạo Thiết bị đầu cuối của Rover.</t>
         </is>
       </c>
     </row>
@@ -28548,7 +28548,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi ngoại hình Terminal của Rover</t>
+          <t>Cậu có thể thay đổi diện mạo Thiết bị đầu cuối của Rover.</t>
         </is>
       </c>
     </row>
@@ -28613,7 +28613,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi ngoại hình Terminal của Rover</t>
+          <t>Cậu có thể thay đổi diện mạo Thiết bị đầu cuối của Rover.</t>
         </is>
       </c>
     </row>
@@ -28678,7 +28678,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi giao diện Terminal của Rover trong trang Resonator Outfits</t>
+          <t>Cậu có thể thay đổi diện mạo Thiết bị đầu cuối của Rover tại trang Trang phục Resonator.</t>
         </is>
       </c>
     </row>
@@ -28743,7 +28743,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>{0} Cậu có thể thay đổi ngoại hình Terminal của Rover trong trang Resonator Trang phục</t>
+          <t>Bạn có thể thay đổi ngoại hình Thiết bị đầu cuối của Rover trong mục Trang Phục Resonator.</t>
         </is>
       </c>
     </row>
@@ -28808,7 +28808,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi giao diện Terminal của Rover trong trang Resonator Outfits</t>
+          <t>Cậu có thể thay đổi diện mạo Thiết bị đầu cuối của Rover tại trang Trang phục Resonator.</t>
         </is>
       </c>
     </row>
@@ -28873,7 +28873,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hoặc thay đổi giao diện Terminal tại đây</t>
+          <t>Bạn có thể xem hoặc thay đổi giao diện Thiết bị đầu cuối tại đây</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hoặc thay đổi giao diện Terminal tại đây</t>
+          <t>Bạn có thể xem hoặc thay đổi giao diện Thiết bị đầu cuối tại đây</t>
         </is>
       </c>
     </row>
@@ -29003,7 +29003,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hoặc thay đổi giao diện Terminal tại đây</t>
+          <t>Bạn có thể xem hoặc thay đổi giao diện Thiết bị đầu cuối tại đây</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Bạn có thể chỉnh sửa dữ liệu Echo tại đây</t>
+          <t>Cậu có thể chỉnh sửa dữ liệu Echo tại đây.</t>
         </is>
       </c>
     </row>
@@ -29133,7 +29133,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bạn có thể chỉnh sửa dữ liệu Echo tại đây</t>
+          <t>Cậu có thể chỉnh sửa dữ liệu Echo tại đây.</t>
         </is>
       </c>
     </row>
@@ -29198,7 +29198,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Bạn có thể chỉnh sửa dữ liệu Echo tại đây</t>
+          <t>Cậu có thể chỉnh sửa dữ liệu Echo tại đây.</t>
         </is>
       </c>
     </row>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>{0} Dùng "Đèn Lồng Napoli Thứ Hai" để phân tách và thay đổi thế giới trong Dark Tide</t>
+          <t>Dùng "Lantern of Napoli the Second" để phân tách và thay đổi các thế giới trong Dark Tide.</t>
         </is>
       </c>
     </row>
@@ -29328,7 +29328,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Dùng "Lồng Đèn Napoli Thứ Hai" để phân tách và thay đổi thế giới trong Dark Tide</t>
+          <t>Dùng "Ngọn Đèn Napoli Đệ Nhị" để phân tách và thay đổi thế giới trong Thủy Triều Hắc Ám</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Throw {0} Lưỡi Dao Lông vào mục tiêu để di chuyển nhanh</t>
+          <t>Ném Lưỡi Kiếm Lông vào mục tiêu để di chuyển nhanh {0}</t>
         </is>
       </c>
     </row>
@@ -29458,7 +29458,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Throw Feather Blade vào mục tiêu để di chuyển nhanh.</t>
+          <t>Ném Lưỡi Kiếm Lông vào mục tiêu để Dịch chuyển nhanh</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>{0} Nắm bắt khoảnh khắc "thế giới" chuyển đổi để tung ra đòn kết liễu và tiêu diệt kẻ địch phía trước</t>
+          <t>{0} Nắm bắt khoảnh khắc "thế giới" chuyển đổi để tung đòn kết liễu và tiêu diệt kẻ địch phía trước.</t>
         </is>
       </c>
     </row>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nắm bắt khoảnh khắc "thế giới" chuyển đổi để tung đòn kết liễu và hạ gục kẻ địch phía trước</t>
+          <t>Nắm bắt khoảnh khắc "thế giới" chuyển đổi để tung đòn kết liễu và tiêu diệt kẻ địch phía trước!</t>
         </is>
       </c>
     </row>
@@ -29653,7 +29653,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Xem kế hoạch nâng cấp Resonators tại đây</t>
+          <t>Bạn có thể xem kế hoạch nâng cấp cho Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -29718,7 +29718,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Xem kế hoạch nâng cấp Resonators tại đây</t>
+          <t>Bạn có thể xem kế hoạch nâng cấp cho Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -29783,7 +29783,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Xem kế hoạch nâng cấp Resonators tại đây</t>
+          <t>Bạn có thể xem kế hoạch nâng cấp cho Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -29848,7 +29848,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn Image Display Mode tại đây.</t>
+          <t>Cậu có thể chọn Chế độ Hiển thị Hình ảnh ở đây.</t>
         </is>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn Image Display Mode tại đây.</t>
+          <t>Cậu có thể chọn Chế độ Hiển thị Hình ảnh ở đây.</t>
         </is>
       </c>
     </row>
@@ -29978,7 +29978,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn Image Display Mode tại đây.</t>
+          <t>Cậu có thể chọn Chế độ Hiển thị Hình ảnh ở đây.</t>
         </is>
       </c>
     </row>
@@ -30043,7 +30043,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Nhấn vào nút "Overworld" để thoát tất cả menu ngay lập tức</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} nút "Overworld" để thoát tất cả menu ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>{0} Giữ nút "Overworld" để thoát tất cả menu ngay lập tức</t>
+          <t>Giữ nút "Thế Giới Mở" để thoát tất cả menu ngay lập tức</t>
         </is>
       </c>
     </row>
@@ -30173,7 +30173,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Nhấn vào nút "Overworld" để thoát tất cả menu ngay lập tức</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} nút "Overworld" để thoát tất cả menu ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Đã mở khóa giao diện Terminal mới. Xem ngay nào!</t>
+          <t>Giao diện Thiết bị đầu cuối mới đã mở khóa. Xem ngay nào!</t>
         </is>
       </c>
     </row>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Switch tab để xem các kế hoạch nâng cấp khác nhau</t>
+          <t>Chuyển tab để xem các kế hoạch nâng cấp khác nhau</t>
         </is>
       </c>
     </row>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Switch tab để xem các kế hoạch nâng cấp khác nhau</t>
+          <t>Chuyển tab để xem các kế hoạch nâng cấp khác nhau</t>
         </is>
       </c>
     </row>
@@ -30433,7 +30433,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Switch tab để xem các kế hoạch nâng cấp khác nhau</t>
+          <t>Chuyển tab để xem các kế hoạch nâng cấp khác nhau</t>
         </is>
       </c>
     </row>
@@ -30498,7 +30498,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu huấn luyện</t>
+          <t>Nhấn vào đây để bắt đầu buổi diễn tập.</t>
         </is>
       </c>
     </row>
@@ -30563,7 +30563,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu huấn luyện</t>
+          <t>Nhấn vào đây để bắt đầu buổi diễn tập.</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu huấn luyện</t>
+          <t>Nhấn vào đây để bắt đầu buổi diễn tập.</t>
         </is>
       </c>
     </row>
@@ -30693,7 +30693,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Một đợt Diễn Tập gồm nhiều đợt chiến đấu</t>
+          <t>Một đợt huấn luyện bao gồm nhiều đợt chiến đấu liên tiếp.</t>
         </is>
       </c>
     </row>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Một đợt Diễn Tập gồm nhiều đợt chiến đấu</t>
+          <t>Một đợt huấn luyện bao gồm nhiều đợt chiến đấu liên tiếp.</t>
         </is>
       </c>
     </row>
@@ -30823,7 +30823,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Một đợt Diễn Tập gồm nhiều đợt chiến đấu</t>
+          <t>Một đợt huấn luyện bao gồm nhiều đợt chiến đấu liên tiếp.</t>
         </is>
       </c>
     </row>
@@ -30888,7 +30888,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Xem Resonator và Vũ khí phù hợp nhất tại đây.</t>
+          <t>Xem Resonator &amp; Vũ Khí phù hợp nhất tại đây</t>
         </is>
       </c>
     </row>
@@ -30953,7 +30953,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Xem Resonator và Vũ khí phù hợp nhất tại đây.</t>
+          <t>Xem Resonator &amp; Vũ Khí phù hợp nhất tại đây</t>
         </is>
       </c>
     </row>
@@ -31018,7 +31018,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Xem Resonator và Vũ khí phù hợp nhất tại đây.</t>
+          <t>Xem Resonator &amp; Vũ Khí phù hợp nhất tại đây</t>
         </is>
       </c>
     </row>
@@ -31083,7 +31083,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Chuẩn bị luyện tập tại đây</t>
+          <t>Chuẩn bị cho buổi luyện tập ở đây nào</t>
         </is>
       </c>
     </row>
@@ -31148,7 +31148,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Chuẩn bị luyện tập tại đây</t>
+          <t>Chuẩn bị cho buổi luyện tập ở đây nào</t>
         </is>
       </c>
     </row>
@@ -31213,7 +31213,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Chuẩn bị luyện tập tại đây</t>
+          <t>Chuẩn bị cho buổi luyện tập ở đây nào</t>
         </is>
       </c>
     </row>
@@ -31473,7 +31473,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Mỗi Resonator sở hữu Vũ Khí khởi đầu khác nhau</t>
+          <t>Mỗi Resonator sở hữu một Vũ Khí khởi đầu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -31538,7 +31538,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Mỗi Resonator sở hữu Vũ Khí khởi đầu khác nhau</t>
+          <t>Mỗi Resonator sở hữu một Vũ Khí khởi đầu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Mỗi Resonator sở hữu Vũ Khí khởi đầu khác nhau</t>
+          <t>Mỗi Resonator sở hữu một Vũ Khí khởi đầu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -31668,7 +31668,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để tiếp tục huấn luyện</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục huấn luyện</t>
         </is>
       </c>
     </row>
@@ -31733,7 +31733,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để tiếp tục huấn luyện</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục huấn luyện</t>
         </is>
       </c>
     </row>
@@ -31798,7 +31798,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để tiếp tục huấn luyện</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục huấn luyện</t>
         </is>
       </c>
     </row>
@@ -31863,7 +31863,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Khi đồng hồ đếm về 0, đợt tấn công kết thúc và cửa hàng mở để mua nâng cấp</t>
+          <t>Khi đồng hồ đếm về 0, đợt tấn công kết thúc và Cửa Hàng mở để mua nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -31928,7 +31928,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi đồng hồ đếm về 0, đợt tấn công kết thúc và cửa hàng mở để mua nâng cấp</t>
+          <t>Khi đồng hồ đếm về 0, đợt tấn công kết thúc và Cửa Hàng mở để mua nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -31993,7 +31993,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khi đồng hồ đếm về 0, đợt tấn công kết thúc và cửa hàng mở để mua nâng cấp</t>
+          <t>Khi đồng hồ đếm về 0, đợt tấn công kết thúc và Cửa Hàng mở để mua nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -32058,7 +32058,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Tiêu hao Enhancement Modules để nâng cấp Weapons, Resonators hoặc mua Vật phẩm</t>
+          <t>Tiêu hao Mô-đun Tăng Cường để nâng cấp Vũ Khí, Resonator hoặc mua vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -32123,7 +32123,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Tiêu hao Enhancement Modules để nâng cấp Weapons, Resonators hoặc mua Vật phẩm</t>
+          <t>Tiêu hao Mô-đun Tăng Cường để nâng cấp Vũ Khí, Resonator hoặc mua vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -32188,7 +32188,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tiêu hao Enhancement Modules để nâng cấp Weapons, Resonators hoặc mua Vật phẩm</t>
+          <t>Tiêu hao Mô-đun Tăng Cường để nâng cấp Vũ Khí, Resonator hoặc mua vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Bạn có thể xem cấp độ của Resonator và Vũ Khí tại đây</t>
+          <t>Bạn có thể xem cấp độ Resonator và Vũ Khí tại đây</t>
         </is>
       </c>
     </row>
@@ -32318,7 +32318,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Bạn có thể xem cấp độ của Resonator và Vũ Khí tại đây</t>
+          <t>Bạn có thể xem cấp độ Resonator và Vũ Khí tại đây</t>
         </is>
       </c>
     </row>
@@ -32383,7 +32383,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Bạn có thể xem cấp độ của Resonator và Vũ Khí tại đây</t>
+          <t>Bạn có thể xem cấp độ Resonator và Vũ Khí tại đây</t>
         </is>
       </c>
     </row>
@@ -32448,7 +32448,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Vật phẩm Locked sẽ được giữ lại khi Shop làm mới</t>
+          <t>Vật phẩm đã khóa sẽ được giữ lại khi Cửa Hàng làm mới lần sau</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>{0}Các vật phẩm bị khóa sẽ được chuyển sang lần làm mới Shop tiếp theo</t>
+          <t>Vật phẩm Đã Khóa sẽ được giữ lại khi Cửa Hàng làm mới</t>
         </is>
       </c>
     </row>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Vật phẩm Locked sẽ được giữ lại khi Shop làm mới</t>
+          <t>Vật phẩm đã khóa sẽ được giữ lại khi Cửa Hàng làm mới lần sau</t>
         </is>
       </c>
     </row>
@@ -32643,7 +32643,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Weapons mới mở khóa ở các đợt nhất định</t>
+          <t>Vũ khí mới mở khóa ở các đợt sóng nhất định</t>
         </is>
       </c>
     </row>
@@ -32708,7 +32708,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Weapons mới mở khóa ở các đợt nhất định</t>
+          <t>Vũ khí mới mở khóa ở các đợt sóng nhất định</t>
         </is>
       </c>
     </row>
@@ -32773,7 +32773,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Weapons mới mở khóa ở các đợt nhất định</t>
+          <t>Vũ khí mới mở khóa ở các đợt sóng nhất định</t>
         </is>
       </c>
     </row>
@@ -32838,7 +32838,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn Weapon mới</t>
+          <t>Cậu có thể chọn một Vũ khí mới.</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32903,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn Weapon mới</t>
+          <t>Cậu có thể chọn một Vũ khí mới.</t>
         </is>
       </c>
     </row>
@@ -32968,7 +32968,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn Weapon mới</t>
+          <t>Cậu có thể chọn một Vũ khí mới.</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33033,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Vũ khí này có thể được hấp thụ để tiến hóa vũ khí khác thành Ultimate Form.</t>
+          <t>Vũ khí này có thể được hấp thụ để tiến hóa một vũ khí khác thành Hình Thái Tối Thượng.</t>
         </is>
       </c>
     </row>
